--- a/saida_skus/SKU_BRINQ-019-VASSOURA-INFANTIL-UNICORNIO.xlsx
+++ b/saida_skus/SKU_BRINQ-019-VASSOURA-INFANTIL-UNICORNIO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -747,8 +747,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n">
-        <v>0</v>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -757,37 +759,39 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,12 +863,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -889,7 +893,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -897,8 +901,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -907,37 +913,39 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,12 +1017,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1050,9 +1058,9 @@
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1082,12 +1090,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,12 +1167,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1198,7 +1206,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1232,12 +1240,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,12 +1317,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1350,9 +1358,9 @@
       <c r="I12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1382,12 +1390,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1459,12 +1467,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1498,11 +1506,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1532,12 +1540,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1609,12 +1617,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1648,7 +1656,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1682,12 +1690,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1759,12 +1767,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1800,9 +1808,9 @@
       <c r="I18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1832,12 +1840,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1909,12 +1917,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1939,7 +1947,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1947,10 +1955,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I20" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1959,39 +1965,37 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2063,12 +2067,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2136,12 +2140,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2213,12 +2217,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2286,12 +2290,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2363,12 +2367,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2393,7 +2397,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2401,47 +2405,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2513,12 +2521,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2552,7 +2560,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -2586,12 +2594,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2663,12 +2671,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2696,17 +2704,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2736,12 +2744,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2813,12 +2821,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2843,7 +2851,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2852,24 +2860,24 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2886,12 +2894,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2963,12 +2971,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2996,17 +3004,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -3036,12 +3044,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3113,12 +3121,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3143,33 +3151,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3186,12 +3194,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3263,12 +3271,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3293,33 +3301,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 312,00</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+          <t>R$ 78,00</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3336,12 +3344,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3413,12 +3421,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3443,33 +3451,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 390,00</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>▼ 4,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3486,12 +3494,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3563,12 +3571,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3593,33 +3601,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 234,00</t>
+          <t>R$ 78,00</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>▼ 49,9%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 28,6%</t>
+        <v>15</v>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3636,12 +3644,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3713,12 +3721,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3743,33 +3751,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 467,00</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>▲ 199,4%</t>
+          <t>R$ 312,00</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>▲ 49,2%</t>
+        <v>0</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3786,12 +3794,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3863,12 +3871,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3893,33 +3901,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 156,00</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 390,00</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>▼ 19,7%</t>
+          <t>▼ 4,6%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3936,12 +3944,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4013,12 +4021,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4052,16 +4060,16 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>▼ 2,6%</t>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
@@ -4069,7 +4077,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4086,12 +4094,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4163,12 +4171,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4196,22 +4204,22 @@
           <t>R$ 467,00</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>▲ 199,4%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 27,1%</t>
+        <v>91</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▲ 49,2%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
@@ -4219,7 +4227,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4236,12 +4244,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4313,12 +4321,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4343,33 +4351,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 545,00</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>▲ 74,7%</t>
+          <t>R$ 156,00</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>107</v>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,3%</t>
+        <v>61</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 19,7%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4386,12 +4394,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4416,7 +4424,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4424,8 +4432,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="n">
-        <v>0</v>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4434,37 +4444,39 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4489,33 +4501,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 312,00</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 234,00</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,9%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>97</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 203,1%</t>
+        <v>76</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 2,6%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4532,12 +4544,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4562,7 +4574,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4570,8 +4582,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="n">
-        <v>0</v>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4580,37 +4594,39 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4635,38 +4651,38 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 467,00</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1500,0%</t>
+        <v>78</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 27,1%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
@@ -4678,12 +4694,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4708,7 +4724,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4716,47 +4732,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4781,33 +4801,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 545,00</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>▲ 74,7%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>2</v>
+        <v>107</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 10,3%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4824,12 +4844,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4857,17 +4877,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4897,12 +4917,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4927,33 +4947,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 312,00</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 99,2%</t>
+        <v>97</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>▲ 203,1%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4970,12 +4990,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5000,7 +5020,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -5009,7 +5029,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -5018,15 +5038,15 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -5043,12 +5063,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5073,38 +5093,38 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 659,00</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 124,9%</t>
+          <t>R$ 78,00</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>120</v>
+        <v>32</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>▲ 4,3%</t>
+          <t>▲ 1500,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
@@ -5116,12 +5136,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5149,9 +5169,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
@@ -5189,12 +5209,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5219,38 +5239,38 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 293,00</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>115</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,2%</t>
+        <v>2</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
@@ -5262,12 +5282,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5292,33 +5312,33 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,5%</t>
+        <v>6</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5335,12 +5355,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5365,33 +5385,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 439,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>131</v>
+        <v>1</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>▼ 0,8%</t>
+          <t>▼ 99,2%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5408,12 +5428,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5438,7 +5458,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 75,00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5447,24 +5467,24 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5481,12 +5501,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5511,33 +5531,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 586,00</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,1%</t>
+          <t>R$ 659,00</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>▲ 124,9%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>▲ 34,7%</t>
+          <t>▲ 4,3%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5554,12 +5574,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5593,11 +5613,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5627,12 +5647,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5657,38 +5677,38 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 659,00</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 80,1%</t>
+          <t>R$ 293,00</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>98</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3,2%</t>
+        <v>115</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,2%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
@@ -5700,12 +5720,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5739,16 +5759,16 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+        <v>7</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
@@ -5773,12 +5793,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5803,29 +5823,29 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 366,00</t>
+          <t>R$ 439,00</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>▼ 61,6%</t>
+          <t>▼ 25,1%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>95</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 13,1%</t>
+        <v>131</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 0,8%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
@@ -5846,12 +5866,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5885,11 +5905,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>▼ 63,2%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5919,12 +5939,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5949,33 +5969,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 952,00</t>
-        </is>
-      </c>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 210,1%</t>
+          <t>R$ 586,00</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>84</v>
+        <v>132</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>▲ 1,2%</t>
+          <t>▲ 34,7%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5992,12 +6012,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6025,17 +6045,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 26,9%</t>
+        <v>10</v>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -6065,12 +6085,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6095,33 +6115,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 307,00</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 659,00</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 80,1%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>98</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3,2%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6138,78 +6158,516 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>R$ 75,00</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 366,00</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 61,6%</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 13,1%</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>5,3%</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 63,2%</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 952,00</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 210,1%</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1,2%</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>15,5%</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>11,3%</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 26,9%</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>BRINQ-019</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>Vassoura infantil unicornio</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 307,00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>6311164080</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>R$ 78,80</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="n">
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="L77" s="2" t="n">
+      <c r="L83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M77" s="2" t="inlineStr">
+      <c r="M83" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="N77" s="2" t="inlineStr">
+      <c r="N83" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O77" s="2" t="inlineStr">
+      <c r="O83" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O77"/>
+  <autoFilter ref="A1:O83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-019-VASSOURA-INFANTIL-UNICORNIO.xlsx
+++ b/saida_skus/SKU_BRINQ-019-VASSOURA-INFANTIL-UNICORNIO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O83"/>
+  <dimension ref="A1:O85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,14 +709,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -739,7 +739,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -747,10 +747,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -759,39 +757,37 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -863,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -940,12 +936,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1017,14 +1013,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -1047,7 +1043,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1055,8 +1051,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I8" s="2" t="n">
-        <v>0</v>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1065,37 +1063,39 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1240,12 +1240,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1390,12 +1390,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1508,9 +1508,9 @@
       <c r="I14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1617,14 +1617,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -1656,11 +1656,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1767,14 +1767,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -1806,11 +1806,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1917,14 +1917,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -1956,11 +1956,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1990,12 +1990,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2067,14 +2067,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2140,12 +2140,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2217,12 +2217,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2290,12 +2290,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2367,14 +2367,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2405,10 +2405,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I26" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -2417,39 +2415,37 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2521,14 +2517,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -2551,7 +2547,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2559,8 +2555,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I28" s="2" t="n">
-        <v>0</v>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -2569,37 +2567,39 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2671,12 +2671,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2821,12 +2821,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2862,9 +2862,9 @@
       <c r="I32" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2894,12 +2894,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2971,14 +2971,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -3010,11 +3010,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3121,14 +3121,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -3154,17 +3154,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3194,12 +3194,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3271,14 +3271,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -3301,33 +3301,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3344,12 +3344,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3421,14 +3421,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -3451,33 +3451,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 78,00</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3571,14 +3571,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -3601,33 +3601,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3721,14 +3721,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -3751,33 +3751,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 312,00</t>
+          <t>R$ 78,00</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>15</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3871,14 +3871,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -3901,33 +3901,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 390,00</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+          <t>R$ 312,00</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>▼ 4,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3944,12 +3944,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4021,14 +4021,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -4051,33 +4051,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 234,00</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,9%</t>
+          <t>R$ 390,00</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>▼ 28,6%</t>
+          <t>▼ 4,6%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4094,12 +4094,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4171,14 +4171,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -4201,33 +4201,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 467,00</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 199,4%</t>
+          <t>R$ 234,00</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,9%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 49,2%</t>
+        <v>65</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4321,14 +4321,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -4351,33 +4351,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 156,00</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 467,00</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>▲ 199,4%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 19,7%</t>
+        <v>91</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>▲ 49,2%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4471,14 +4471,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -4501,33 +4501,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 234,00</t>
+          <t>R$ 156,00</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>▼ 49,9%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>▼ 2,6%</t>
+          <t>▼ 19,7%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4621,14 +4621,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -4651,33 +4651,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 467,00</t>
+          <t>R$ 234,00</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 49,9%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>▼ 27,1%</t>
+          <t>▼ 2,6%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4771,14 +4771,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -4801,33 +4801,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 545,00</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 74,7%</t>
+          <t>R$ 467,00</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>107</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,3%</t>
+        <v>78</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 27,1%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4844,14 +4844,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -4874,7 +4874,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4882,8 +4882,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="n">
-        <v>0</v>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
@@ -4892,39 +4894,41 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -4947,33 +4951,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 312,00</t>
+          <t>R$ 545,00</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▲ 74,7%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>▲ 203,1%</t>
+          <t>▲ 10,3%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4990,12 +4994,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5063,14 +5067,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -5093,38 +5097,38 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 312,00</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>▲ 1500,0%</t>
+          <t>▲ 203,1%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
@@ -5136,12 +5140,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5177,9 +5181,9 @@
       <c r="I63" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5209,14 +5213,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -5239,7 +5243,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 78,00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5248,29 +5252,29 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 1500,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
@@ -5282,14 +5286,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -5315,17 +5319,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H65" s="3" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5355,14 +5359,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -5388,17 +5392,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 99,2%</t>
+        <v>2</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5428,14 +5432,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -5458,33 +5462,33 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5501,14 +5505,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -5531,33 +5535,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 659,00</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 124,9%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 4,3%</t>
+        <v>1</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 99,2%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5574,14 +5578,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -5604,33 +5608,33 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 75,00</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5647,14 +5651,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -5677,38 +5681,38 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 293,00</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 659,00</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 124,9%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>115</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,2%</t>
+        <v>120</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 4,3%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
@@ -5720,14 +5724,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -5750,33 +5754,33 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>▼ 12,5%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5793,14 +5797,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -5823,38 +5827,38 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 439,00</t>
+          <t>R$ 293,00</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,1%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>▼ 0,8%</t>
+          <t>▼ 12,2%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
@@ -5866,14 +5870,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -5896,7 +5900,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 75,00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5905,24 +5909,24 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5939,14 +5943,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -5969,33 +5973,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 586,00</t>
+          <t>R$ 439,00</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>▼ 11,1%</t>
+          <t>▼ 25,1%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>132</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 34,7%</t>
+        <v>131</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 0,8%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6012,14 +6016,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -6045,17 +6049,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -6085,14 +6089,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -6115,33 +6119,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 659,00</t>
-        </is>
-      </c>
-      <c r="H76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 80,1%</t>
+          <t>R$ 586,00</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>▲ 3,2%</t>
+          <t>▲ 34,7%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6158,14 +6162,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -6188,33 +6192,33 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6231,14 +6235,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -6261,33 +6265,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 366,00</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 61,6%</t>
+          <t>R$ 659,00</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 80,1%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>▲ 13,1%</t>
+          <t>▲ 3,2%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6304,14 +6308,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -6334,7 +6338,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 75,00</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6343,24 +6347,24 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 63,2%</t>
+        <v>8</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6377,14 +6381,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -6407,33 +6411,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 952,00</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 210,1%</t>
+          <t>R$ 366,00</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 61,6%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>▲ 1,2%</t>
+          <t>▲ 13,1%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6450,14 +6454,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -6489,11 +6493,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>▼ 26,9%</t>
+          <t>▼ 63,2%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6523,14 +6527,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -6553,33 +6557,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 307,00</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 952,00</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 210,1%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>84</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1,2%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6596,14 +6600,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -6635,11 +6639,11 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>19</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 26,9%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6666,8 +6670,154 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 307,00</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O83"/>
+  <autoFilter ref="A1:O85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-019-VASSOURA-INFANTIL-UNICORNIO.xlsx
+++ b/saida_skus/SKU_BRINQ-019-VASSOURA-INFANTIL-UNICORNIO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O85"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -747,8 +747,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n">
-        <v>0</v>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -757,37 +759,39 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,12 +863,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -889,7 +893,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -897,10 +901,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -909,39 +911,37 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1013,12 +1013,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1051,10 +1051,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1063,39 +1061,37 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1167,12 +1163,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1240,12 +1236,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1317,12 +1313,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1347,7 +1343,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1355,8 +1351,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="2" t="n">
-        <v>0</v>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1365,37 +1363,39 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1505,8 +1505,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I14" s="2" t="n">
-        <v>0</v>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1515,37 +1517,39 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1617,12 +1621,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1658,9 +1662,9 @@
       <c r="I16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1690,12 +1694,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1767,12 +1771,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1806,7 +1810,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1840,12 +1844,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1917,12 +1921,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1958,9 +1962,9 @@
       <c r="I20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1990,12 +1994,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2067,12 +2071,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2106,11 +2110,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2140,12 +2144,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2217,12 +2221,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2256,7 +2260,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -2290,12 +2294,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2367,12 +2371,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2408,9 +2412,9 @@
       <c r="I26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2440,12 +2444,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2517,12 +2521,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2547,7 +2551,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2555,10 +2559,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I28" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -2567,39 +2569,37 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2671,12 +2671,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2821,12 +2821,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2894,12 +2894,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3009,47 +3009,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3121,12 +3125,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3160,7 +3164,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -3194,12 +3198,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3271,12 +3275,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3304,17 +3308,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3344,12 +3348,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3421,12 +3425,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3451,7 +3455,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3460,24 +3464,24 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3494,12 +3498,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3571,12 +3575,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3604,17 +3608,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3644,12 +3648,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3721,12 +3725,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3751,33 +3755,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3794,12 +3798,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3871,12 +3875,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3901,33 +3905,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 312,00</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+          <t>R$ 78,00</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3944,12 +3948,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4021,12 +4025,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4051,33 +4055,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 390,00</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>▼ 4,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4094,12 +4098,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4171,12 +4175,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4201,33 +4205,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 234,00</t>
+          <t>R$ 78,00</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>▼ 49,9%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 28,6%</t>
+        <v>15</v>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4244,12 +4248,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4321,12 +4325,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4351,33 +4355,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 467,00</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>▲ 199,4%</t>
+          <t>R$ 312,00</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>▲ 49,2%</t>
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4394,12 +4398,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4471,12 +4475,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4501,33 +4505,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 156,00</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 390,00</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>▼ 19,7%</t>
+          <t>▼ 4,6%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4544,12 +4548,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4621,12 +4625,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4660,16 +4664,16 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>▼ 2,6%</t>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
@@ -4677,7 +4681,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4694,12 +4698,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4771,12 +4775,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4804,22 +4808,22 @@
           <t>R$ 467,00</t>
         </is>
       </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>▲ 199,4%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 27,1%</t>
+        <v>91</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▲ 49,2%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
@@ -4827,7 +4831,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4844,12 +4848,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4921,12 +4925,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4951,33 +4955,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 545,00</t>
-        </is>
-      </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>▲ 74,7%</t>
+          <t>R$ 156,00</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>107</v>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,3%</t>
+        <v>61</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 19,7%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4994,12 +4998,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5024,7 +5028,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -5032,8 +5036,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="n">
-        <v>0</v>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -5042,37 +5048,39 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5097,33 +5105,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 312,00</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 234,00</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,9%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>97</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 203,1%</t>
+        <v>76</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 2,6%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5140,12 +5148,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5170,7 +5178,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5178,8 +5186,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="n">
-        <v>0</v>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5188,37 +5198,39 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5243,38 +5255,38 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 467,00</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1500,0%</t>
+        <v>78</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 27,1%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
@@ -5286,12 +5298,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5316,7 +5328,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5324,47 +5336,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5389,33 +5405,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 545,00</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>▲ 74,7%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>2</v>
+        <v>107</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 10,3%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5432,12 +5448,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5465,17 +5481,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5505,12 +5521,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5535,33 +5551,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 312,00</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 99,2%</t>
+        <v>97</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>▲ 203,1%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5578,12 +5594,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5608,7 +5624,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5617,7 +5633,7 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -5626,15 +5642,15 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5651,12 +5667,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5681,38 +5697,38 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 659,00</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 124,9%</t>
+          <t>R$ 78,00</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>120</v>
+        <v>32</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>▲ 4,3%</t>
+          <t>▲ 1500,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
@@ -5724,12 +5740,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5757,9 +5773,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
@@ -5797,12 +5813,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5827,38 +5843,38 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 293,00</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>115</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,2%</t>
+        <v>2</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
@@ -5870,12 +5886,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5900,33 +5916,33 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,5%</t>
+        <v>6</v>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5943,12 +5959,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5973,33 +5989,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 439,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>131</v>
+        <v>1</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>▼ 0,8%</t>
+          <t>▼ 99,2%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6016,12 +6032,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6046,7 +6062,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 75,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6055,24 +6071,24 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -6089,12 +6105,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6119,33 +6135,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 586,00</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,1%</t>
+          <t>R$ 659,00</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 124,9%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>▲ 34,7%</t>
+          <t>▲ 4,3%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6162,12 +6178,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6201,11 +6217,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6235,12 +6251,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6265,38 +6281,38 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 659,00</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 80,1%</t>
+          <t>R$ 293,00</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>98</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3,2%</t>
+        <v>115</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,2%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
@@ -6308,12 +6324,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6347,16 +6363,16 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+        <v>7</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
@@ -6381,12 +6397,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6411,29 +6427,29 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 366,00</t>
+          <t>R$ 439,00</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>▼ 61,6%</t>
+          <t>▼ 25,1%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>95</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 13,1%</t>
+        <v>131</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 0,8%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
@@ -6454,12 +6470,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6493,11 +6509,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>▼ 63,2%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6527,12 +6543,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6557,33 +6573,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 952,00</t>
-        </is>
-      </c>
-      <c r="H82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 210,1%</t>
+          <t>R$ 586,00</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>84</v>
+        <v>132</v>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>▲ 1,2%</t>
+          <t>▲ 34,7%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6600,12 +6616,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6633,17 +6649,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 26,9%</t>
+        <v>10</v>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6673,12 +6689,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6703,33 +6719,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 307,00</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 659,00</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 80,1%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>98</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3,2%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6746,78 +6762,516 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 75,00</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 366,00</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 61,6%</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 13,1%</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>5,3%</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 63,2%</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 952,00</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>▲ 210,1%</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1,2%</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>15,5%</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>11,3%</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 26,9%</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>BRINQ-019</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Vassoura infantil unicornio</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 307,00</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>6311164080</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>R$ 78,80</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="n">
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr">
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="L85" s="2" t="n">
+      <c r="L91" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M85" s="2" t="inlineStr">
+      <c r="M91" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="N85" s="2" t="inlineStr">
+      <c r="N91" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O85" s="2" t="inlineStr">
+      <c r="O91" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O85"/>
+  <autoFilter ref="A1:O91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-019-VASSOURA-INFANTIL-UNICORNIO.xlsx
+++ b/saida_skus/SKU_BRINQ-019-VASSOURA-INFANTIL-UNICORNIO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -747,10 +747,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -759,39 +757,37 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -863,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -936,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1013,12 +1009,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1086,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1163,12 +1159,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1193,7 +1189,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1201,8 +1197,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="2" t="n">
-        <v>0</v>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1211,37 +1209,39 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1351,10 +1351,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I12" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1363,39 +1361,37 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1467,12 +1463,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1497,7 +1493,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1505,10 +1501,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I14" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1517,39 +1511,37 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1621,12 +1613,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1694,12 +1686,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1771,12 +1763,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1801,7 +1793,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1809,8 +1801,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="2" t="n">
-        <v>0</v>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1819,37 +1813,39 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1921,12 +1917,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1951,7 +1947,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1959,8 +1955,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="2" t="n">
-        <v>0</v>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1969,37 +1967,39 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2071,12 +2071,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2112,9 +2112,9 @@
       <c r="I22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2221,12 +2221,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2260,7 +2260,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -2294,12 +2294,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2412,9 +2412,9 @@
       <c r="I26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2444,12 +2444,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2560,11 +2560,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2671,12 +2671,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -2744,12 +2744,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2821,12 +2821,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2862,9 +2862,9 @@
       <c r="I32" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2894,12 +2894,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3009,10 +3009,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I34" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -3021,39 +3019,37 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3125,12 +3121,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3198,12 +3194,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3275,12 +3271,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3348,12 +3344,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3425,12 +3421,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3455,7 +3451,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3463,47 +3459,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3575,12 +3575,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3614,7 +3614,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -3648,12 +3648,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3758,17 +3758,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3798,12 +3798,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3914,24 +3914,24 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4025,12 +4025,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4058,17 +4058,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4098,12 +4098,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4205,33 +4205,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4248,12 +4248,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4355,33 +4355,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 312,00</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+          <t>R$ 78,00</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4475,12 +4475,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4505,33 +4505,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 390,00</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>▼ 4,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4548,12 +4548,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4625,12 +4625,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4655,33 +4655,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 234,00</t>
+          <t>R$ 78,00</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>▼ 49,9%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 28,6%</t>
+        <v>15</v>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4805,33 +4805,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 467,00</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 199,4%</t>
+          <t>R$ 312,00</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 49,2%</t>
+        <v>0</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4848,12 +4848,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4955,33 +4955,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 156,00</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 390,00</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>▼ 19,7%</t>
+          <t>▼ 4,6%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5114,16 +5114,16 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>▼ 2,6%</t>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5148,12 +5148,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5225,12 +5225,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5258,22 +5258,22 @@
           <t>R$ 467,00</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 199,4%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 27,1%</t>
+        <v>91</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 49,2%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5375,12 +5375,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5405,33 +5405,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 545,00</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 74,7%</t>
+          <t>R$ 156,00</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>107</v>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,3%</t>
+        <v>61</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 19,7%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5448,12 +5448,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5486,8 +5486,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="n">
-        <v>0</v>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5496,37 +5498,39 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5551,33 +5555,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 312,00</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 234,00</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,9%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>97</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 203,1%</t>
+        <v>76</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 2,6%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5594,12 +5598,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5624,7 +5628,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5632,8 +5636,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="n">
-        <v>0</v>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -5642,37 +5648,39 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5697,38 +5705,38 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 467,00</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1500,0%</t>
+        <v>78</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 27,1%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
@@ -5740,12 +5748,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5770,7 +5778,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5778,47 +5786,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5843,33 +5855,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 545,00</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 74,7%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>2</v>
+        <v>107</v>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 10,3%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5886,12 +5898,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5919,17 +5931,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5959,12 +5971,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5989,33 +6001,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 312,00</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 99,2%</t>
+        <v>97</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 203,1%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6032,12 +6044,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6062,7 +6074,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6071,7 +6083,7 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -6080,15 +6092,15 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -6105,12 +6117,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6135,38 +6147,38 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 659,00</t>
-        </is>
-      </c>
-      <c r="H76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 124,9%</t>
+          <t>R$ 78,00</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>120</v>
+        <v>32</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>▲ 4,3%</t>
+          <t>▲ 1500,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
@@ -6178,12 +6190,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6211,9 +6223,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
@@ -6251,12 +6263,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6281,38 +6293,38 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 293,00</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>115</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,2%</t>
+        <v>2</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
@@ -6324,12 +6336,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6354,33 +6366,33 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,5%</t>
+        <v>6</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6397,12 +6409,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6427,33 +6439,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 439,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>131</v>
+        <v>1</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>▼ 0,8%</t>
+          <t>▼ 99,2%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6470,12 +6482,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6500,7 +6512,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 75,00</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6509,24 +6521,24 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6543,12 +6555,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6573,33 +6585,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 586,00</t>
-        </is>
-      </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,1%</t>
+          <t>R$ 659,00</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 124,9%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>▲ 34,7%</t>
+          <t>▲ 4,3%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6616,12 +6628,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6655,11 +6667,11 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J83" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6689,12 +6701,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6719,38 +6731,38 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 659,00</t>
-        </is>
-      </c>
-      <c r="H84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 80,1%</t>
+          <t>R$ 293,00</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>98</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3,2%</t>
+        <v>115</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,2%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
@@ -6762,12 +6774,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6801,16 +6813,16 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J85" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+        <v>7</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
@@ -6835,12 +6847,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6865,29 +6877,29 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 366,00</t>
+          <t>R$ 439,00</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>▼ 61,6%</t>
+          <t>▼ 25,1%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>95</v>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>▲ 13,1%</t>
+        <v>131</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 0,8%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
@@ -6908,12 +6920,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6947,11 +6959,11 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>▼ 63,2%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6981,12 +6993,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7011,33 +7023,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 952,00</t>
-        </is>
-      </c>
-      <c r="H88" s="4" t="inlineStr">
-        <is>
-          <t>▲ 210,1%</t>
+          <t>R$ 586,00</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>84</v>
+        <v>132</v>
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>▲ 1,2%</t>
+          <t>▲ 34,7%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -7054,12 +7066,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7087,17 +7099,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 26,9%</t>
+        <v>10</v>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7127,12 +7139,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7157,33 +7169,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 307,00</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 659,00</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>▲ 80,1%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>98</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3,2%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7200,78 +7212,516 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 75,00</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 366,00</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 61,6%</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>▲ 13,1%</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>5,3%</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>▼ 63,2%</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 952,00</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>▲ 210,1%</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1,2%</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>15,5%</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>11,3%</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 26,9%</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>BRINQ-019</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>Vassoura infantil unicornio</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 307,00</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>6311164080</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>R$ 78,80</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="n">
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K91" s="2" t="inlineStr">
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="L91" s="2" t="n">
+      <c r="L97" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M91" s="2" t="inlineStr">
+      <c r="M97" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="N91" s="2" t="inlineStr">
+      <c r="N97" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O91" s="2" t="inlineStr">
+      <c r="O97" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O91"/>
+  <autoFilter ref="A1:O97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-019-VASSOURA-INFANTIL-UNICORNIO.xlsx
+++ b/saida_skus/SKU_BRINQ-019-VASSOURA-INFANTIL-UNICORNIO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O97"/>
+  <dimension ref="A1:O99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,14 +709,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,14 +1159,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1197,10 +1197,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1209,39 +1207,37 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1313,14 +1309,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -1343,7 +1339,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1351,8 +1347,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="2" t="n">
-        <v>0</v>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1361,37 +1359,39 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1536,12 +1536,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1686,12 +1686,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1763,14 +1763,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1801,10 +1801,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I18" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1813,39 +1811,37 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1917,12 +1913,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1994,12 +1990,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2071,14 +2067,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -2101,7 +2097,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2109,8 +2105,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I22" s="2" t="n">
-        <v>0</v>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2119,37 +2117,39 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2221,12 +2221,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2444,12 +2444,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2562,9 +2562,9 @@
       <c r="I28" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2671,14 +2671,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -2710,11 +2710,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2821,14 +2821,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -2860,11 +2860,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2894,12 +2894,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2971,14 +2971,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -3010,11 +3010,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3121,14 +3121,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -3194,12 +3194,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3344,12 +3344,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3421,14 +3421,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3459,10 +3459,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I40" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -3471,39 +3469,37 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3575,14 +3571,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -3605,7 +3601,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3613,8 +3609,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I42" s="2" t="n">
-        <v>0</v>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -3623,37 +3621,39 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3798,12 +3798,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3916,9 +3916,9 @@
       <c r="I46" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4025,14 +4025,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -4064,11 +4064,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4098,12 +4098,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4175,14 +4175,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -4208,17 +4208,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4248,12 +4248,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4325,14 +4325,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -4355,33 +4355,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4475,14 +4475,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -4505,33 +4505,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 78,00</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4548,12 +4548,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4625,14 +4625,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -4655,33 +4655,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4775,14 +4775,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -4805,33 +4805,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 312,00</t>
+          <t>R$ 78,00</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>15</v>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4848,12 +4848,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4925,14 +4925,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -4955,33 +4955,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 390,00</t>
-        </is>
-      </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+          <t>R$ 312,00</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>▼ 4,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5075,14 +5075,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -5105,33 +5105,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 234,00</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,9%</t>
+          <t>R$ 390,00</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>▼ 28,6%</t>
+          <t>▼ 4,6%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5148,12 +5148,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5225,14 +5225,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -5255,33 +5255,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 467,00</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="inlineStr">
-        <is>
-          <t>▲ 199,4%</t>
+          <t>R$ 234,00</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,9%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▲ 49,2%</t>
+        <v>65</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5375,14 +5375,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -5405,33 +5405,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 156,00</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 467,00</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>▲ 199,4%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 19,7%</t>
+        <v>91</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>▲ 49,2%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5448,12 +5448,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5525,14 +5525,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -5555,33 +5555,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 234,00</t>
+          <t>R$ 156,00</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>▼ 49,9%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>▼ 2,6%</t>
+          <t>▼ 19,7%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5675,14 +5675,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -5705,33 +5705,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 467,00</t>
+          <t>R$ 234,00</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 49,9%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>▼ 27,1%</t>
+          <t>▼ 2,6%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5748,12 +5748,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5825,14 +5825,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -5855,33 +5855,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 545,00</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 74,7%</t>
+          <t>R$ 467,00</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>107</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,3%</t>
+        <v>78</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 27,1%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5898,14 +5898,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -5928,7 +5928,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5936,8 +5936,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="n">
-        <v>0</v>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
@@ -5946,39 +5948,41 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -6001,33 +6005,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 312,00</t>
+          <t>R$ 545,00</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▲ 74,7%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>▲ 203,1%</t>
+          <t>▲ 10,3%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6044,12 +6048,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6117,14 +6121,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -6147,38 +6151,38 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 312,00</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>▲ 1500,0%</t>
+          <t>▲ 203,1%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
@@ -6190,12 +6194,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6231,9 +6235,9 @@
       <c r="I77" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6263,14 +6267,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -6293,7 +6297,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 78,00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6302,29 +6306,29 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 1500,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
@@ -6336,14 +6340,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -6369,17 +6373,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H79" s="3" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6409,14 +6413,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -6442,17 +6446,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 99,2%</t>
+        <v>2</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6482,14 +6486,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -6512,33 +6516,33 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6555,14 +6559,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -6585,33 +6589,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 659,00</t>
-        </is>
-      </c>
-      <c r="H82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 124,9%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 4,3%</t>
+        <v>1</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 99,2%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6628,14 +6632,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -6658,33 +6662,33 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 75,00</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6701,14 +6705,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -6731,38 +6735,38 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 293,00</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 659,00</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 124,9%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>115</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,2%</t>
+        <v>120</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 4,3%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
@@ -6774,14 +6778,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -6804,33 +6808,33 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>▼ 12,5%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -6847,14 +6851,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -6877,38 +6881,38 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 439,00</t>
+          <t>R$ 293,00</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,1%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>▼ 0,8%</t>
+          <t>▼ 12,2%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
@@ -6920,14 +6924,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -6950,7 +6954,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 75,00</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6959,24 +6963,24 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -6993,14 +6997,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -7023,33 +7027,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 586,00</t>
+          <t>R$ 439,00</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>▼ 11,1%</t>
+          <t>▼ 25,1%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>132</v>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>▲ 34,7%</t>
+        <v>131</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 0,8%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -7066,14 +7070,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -7099,17 +7103,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J89" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7139,14 +7143,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -7169,33 +7173,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 659,00</t>
-        </is>
-      </c>
-      <c r="H90" s="4" t="inlineStr">
-        <is>
-          <t>▲ 80,1%</t>
+          <t>R$ 586,00</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>▲ 3,2%</t>
+          <t>▲ 34,7%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7212,14 +7216,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -7242,33 +7246,33 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -7285,14 +7289,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -7315,33 +7319,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 366,00</t>
-        </is>
-      </c>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 61,6%</t>
+          <t>R$ 659,00</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>▲ 80,1%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>▲ 13,1%</t>
+          <t>▲ 3,2%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7358,14 +7362,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -7388,7 +7392,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 75,00</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7397,24 +7401,24 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J93" s="3" t="inlineStr">
-        <is>
-          <t>▼ 63,2%</t>
+        <v>8</v>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7431,14 +7435,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -7461,33 +7465,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 952,00</t>
-        </is>
-      </c>
-      <c r="H94" s="4" t="inlineStr">
-        <is>
-          <t>▲ 210,1%</t>
+          <t>R$ 366,00</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 61,6%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>▲ 1,2%</t>
+          <t>▲ 13,1%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7504,14 +7508,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -7543,11 +7547,11 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>▼ 26,9%</t>
+          <t>▼ 63,2%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7577,14 +7581,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -7607,33 +7611,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 307,00</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 952,00</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>▲ 210,1%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>84</v>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1,2%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7650,14 +7654,14 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -7689,11 +7693,11 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>19</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 26,9%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7720,8 +7724,154 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 307,00</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O97"/>
+  <autoFilter ref="A1:O99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-019-VASSOURA-INFANTIL-UNICORNIO.xlsx
+++ b/saida_skus/SKU_BRINQ-019-VASSOURA-INFANTIL-UNICORNIO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:O103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -900,9 +900,9 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1082,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,12 +1309,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1347,10 +1347,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I12" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1359,39 +1357,37 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1463,12 +1459,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1536,12 +1532,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1613,12 +1609,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1643,7 +1639,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1651,8 +1647,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I16" s="2" t="n">
-        <v>0</v>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1661,37 +1659,39 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1763,12 +1763,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1913,12 +1913,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1951,10 +1951,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I20" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1963,39 +1961,37 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2067,12 +2063,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2097,7 +2093,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2105,10 +2101,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I22" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2117,39 +2111,37 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2221,12 +2213,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2251,7 +2243,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2259,8 +2251,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I24" s="2" t="n">
-        <v>0</v>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -2269,37 +2263,39 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2371,12 +2367,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2401,7 +2397,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2409,8 +2405,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I26" s="2" t="n">
-        <v>0</v>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -2419,37 +2417,39 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2671,12 +2671,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2712,9 +2712,9 @@
       <c r="I30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2821,12 +2821,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2860,7 +2860,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2894,12 +2894,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3121,12 +3121,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3194,12 +3194,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3312,9 +3312,9 @@
       <c r="I38" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3344,12 +3344,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3421,12 +3421,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3460,7 +3460,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -3494,12 +3494,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3571,12 +3571,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3609,10 +3609,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I42" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -3621,39 +3619,37 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3725,12 +3721,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3798,12 +3794,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3875,12 +3871,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3905,7 +3901,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3913,8 +3909,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I46" s="2" t="n">
-        <v>0</v>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3923,37 +3921,39 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4025,12 +4025,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4066,9 +4066,9 @@
       <c r="I48" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4098,12 +4098,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4248,12 +4248,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4358,9 +4358,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
@@ -4398,12 +4398,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4475,12 +4475,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -4523,15 +4523,15 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4548,12 +4548,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4625,12 +4625,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4808,13 +4808,13 @@
           <t>R$ 78,00</t>
         </is>
       </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4848,12 +4848,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4955,12 +4955,12 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 312,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
@@ -4977,11 +4977,11 @@
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5105,33 +5105,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 390,00</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+          <t>R$ 78,00</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,6%</t>
+        <v>15</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5148,12 +5148,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5225,12 +5225,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5255,33 +5255,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 234,00</t>
+          <t>R$ 312,00</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>▼ 49,9%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>▼ 28,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5375,12 +5375,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5405,33 +5405,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 467,00</t>
+          <t>R$ 390,00</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>▲ 199,4%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 49,2%</t>
+        <v>62</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,6%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5448,12 +5448,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5555,33 +5555,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 156,00</t>
+          <t>R$ 234,00</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 49,9%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>▼ 19,7%</t>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5705,33 +5705,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 234,00</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,9%</t>
+          <t>R$ 467,00</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 199,4%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>76</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 2,6%</t>
+        <v>91</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 49,2%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5748,12 +5748,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5855,33 +5855,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 467,00</t>
+          <t>R$ 156,00</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>▼ 27,1%</t>
+          <t>▼ 19,7%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6005,33 +6005,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 545,00</t>
-        </is>
-      </c>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 74,7%</t>
+          <t>R$ 234,00</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,9%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>107</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,3%</t>
+        <v>76</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 2,6%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6086,8 +6086,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="n">
-        <v>0</v>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -6096,37 +6098,39 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6151,33 +6155,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 312,00</t>
-        </is>
-      </c>
-      <c r="H76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 467,00</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>97</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 203,1%</t>
+        <v>78</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 27,1%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6194,12 +6198,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6224,7 +6228,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6232,8 +6236,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="n">
-        <v>0</v>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -6242,37 +6248,39 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6297,38 +6305,38 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 545,00</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 74,7%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>▲ 1500,0%</t>
+          <t>▲ 10,3%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
@@ -6340,12 +6348,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6381,9 +6389,9 @@
       <c r="I79" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6413,12 +6421,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6443,33 +6451,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 312,00</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>2</v>
+        <v>97</v>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 203,1%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6486,12 +6494,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6519,17 +6527,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6559,12 +6567,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6589,38 +6597,38 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 78,00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1500,0%</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>3,1%</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 99,2%</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
@@ -6632,12 +6640,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6662,7 +6670,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6671,24 +6679,24 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6705,12 +6713,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6735,33 +6743,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 659,00</t>
-        </is>
-      </c>
-      <c r="H84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 124,9%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>120</v>
+        <v>2</v>
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>▲ 4,3%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6778,12 +6786,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6817,11 +6825,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6851,12 +6859,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6881,38 +6889,38 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 293,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>115</v>
+        <v>1</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>▼ 12,2%</t>
+          <t>▼ 99,2%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
@@ -6924,12 +6932,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6963,16 +6971,16 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,5%</t>
+        <v>2</v>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
@@ -6980,7 +6988,7 @@
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -6997,12 +7005,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7027,33 +7035,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 439,00</t>
-        </is>
-      </c>
-      <c r="H88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,1%</t>
+          <t>R$ 659,00</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>▲ 124,9%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>131</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 0,8%</t>
+        <v>120</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>▲ 4,3%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -7070,12 +7078,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7103,17 +7111,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7143,12 +7151,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7173,38 +7181,38 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 586,00</t>
+          <t>R$ 293,00</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>▼ 11,1%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>132</v>
-      </c>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t>▲ 34,7%</t>
+        <v>115</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,2%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
@@ -7216,12 +7224,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7246,33 +7254,33 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H91" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 75,00</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J91" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -7289,12 +7297,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7319,33 +7327,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 659,00</t>
-        </is>
-      </c>
-      <c r="H92" s="4" t="inlineStr">
-        <is>
-          <t>▲ 80,1%</t>
+          <t>R$ 439,00</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,1%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>98</v>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3,2%</t>
+        <v>131</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 0,8%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7362,12 +7370,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7392,7 +7400,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7403,22 +7411,22 @@
       <c r="I93" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J93" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7435,12 +7443,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7465,33 +7473,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 366,00</t>
+          <t>R$ 586,00</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>▼ 61,6%</t>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>95</v>
+        <v>132</v>
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>▲ 13,1%</t>
+          <t>▲ 34,7%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7508,12 +7516,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7541,17 +7549,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>▼ 63,2%</t>
+        <v>10</v>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7581,12 +7589,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7611,33 +7619,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 952,00</t>
+          <t>R$ 659,00</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>▲ 210,1%</t>
+          <t>▲ 80,1%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>▲ 1,2%</t>
+          <t>▲ 3,2%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7654,12 +7662,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7684,7 +7692,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 75,00</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7693,24 +7701,24 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>▼ 26,9%</t>
+        <v>8</v>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -7727,12 +7735,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7757,33 +7765,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 307,00</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 366,00</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 61,6%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>95</v>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>▲ 13,1%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
+          <t>5,3%</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
           <t>4,8%</t>
-        </is>
-      </c>
-      <c r="L98" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="M98" s="2" t="inlineStr">
-        <is>
-          <t>3,3%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7800,12 +7808,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7839,11 +7847,11 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>▼ 63,2%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7870,8 +7878,300 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 952,00</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>▲ 210,1%</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1,2%</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>15,5%</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>11,3%</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>▼ 26,9%</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 307,00</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O99"/>
+  <autoFilter ref="A1:O103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-019-VASSOURA-INFANTIL-UNICORNIO.xlsx
+++ b/saida_skus/SKU_BRINQ-019-VASSOURA-INFANTIL-UNICORNIO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O103"/>
+  <dimension ref="A1:O127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -597,47 +597,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,12 +713,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -739,7 +743,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -747,8 +751,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n">
-        <v>1</v>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -757,37 +763,39 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,12 +867,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -900,9 +908,9 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -932,12 +940,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,12 +1017,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1039,7 +1047,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1047,8 +1055,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I8" s="2" t="n">
-        <v>1</v>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1057,37 +1067,39 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,12 +1171,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1189,7 +1201,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1197,8 +1209,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="2" t="n">
-        <v>0</v>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1207,37 +1221,39 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,12 +1325,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1339,7 +1355,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1347,8 +1363,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="2" t="n">
-        <v>0</v>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1357,37 +1375,39 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1459,12 +1479,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1532,12 +1552,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1609,12 +1629,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1639,7 +1659,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1647,10 +1667,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I16" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1659,39 +1677,37 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1763,12 +1779,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1836,12 +1852,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1913,12 +1929,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1986,12 +2002,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2063,12 +2079,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2093,7 +2109,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2101,8 +2117,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I22" s="2" t="n">
-        <v>0</v>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2111,37 +2129,39 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2213,12 +2233,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2243,7 +2263,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2251,10 +2271,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I24" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -2263,39 +2281,37 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2367,12 +2383,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2397,7 +2413,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2405,51 +2421,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2521,12 +2533,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2560,7 +2572,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -2594,12 +2606,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2671,12 +2683,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2712,9 +2724,9 @@
       <c r="I30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2744,12 +2756,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2821,12 +2833,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2860,7 +2872,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2894,12 +2906,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2971,12 +2983,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3012,9 +3024,9 @@
       <c r="I34" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -3044,12 +3056,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3121,12 +3133,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3160,7 +3172,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -3194,12 +3206,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3271,12 +3283,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3312,9 +3324,9 @@
       <c r="I38" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3344,12 +3356,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3421,12 +3433,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3451,7 +3463,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3459,8 +3471,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I40" s="2" t="n">
-        <v>1</v>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -3469,37 +3483,39 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3571,12 +3587,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3644,12 +3660,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3721,12 +3737,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3794,12 +3810,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3871,12 +3887,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3901,7 +3917,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3909,10 +3925,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I46" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3921,39 +3935,37 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4025,12 +4037,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4055,7 +4067,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4063,8 +4075,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I48" s="2" t="n">
-        <v>0</v>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -4073,37 +4087,39 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4175,12 +4191,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4205,7 +4221,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4213,8 +4229,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="2" t="n">
-        <v>0</v>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4223,37 +4241,39 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4325,12 +4345,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4366,9 +4386,9 @@
       <c r="I52" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4398,12 +4418,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4475,12 +4495,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4514,7 +4534,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -4548,12 +4568,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4625,12 +4645,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4658,17 +4678,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4698,12 +4718,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4775,12 +4795,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4805,7 +4825,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4814,24 +4834,24 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4848,12 +4868,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4925,12 +4945,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4958,17 +4978,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4998,12 +5018,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5075,12 +5095,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5105,33 +5125,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5148,12 +5168,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5225,12 +5245,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5255,33 +5275,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 312,00</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
+      <c r="M64" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="M64" s="2" t="inlineStr">
-        <is>
-          <t>4,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5298,12 +5318,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5375,12 +5395,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5405,33 +5425,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 390,00</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,6%</t>
+        <v>0</v>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5448,12 +5468,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5525,12 +5545,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5555,33 +5575,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 234,00</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,9%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 28,6%</t>
+        <v>0</v>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5598,12 +5618,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5675,12 +5695,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5705,55 +5725,59 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 467,00</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 199,4%</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 49,2%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="n">
-        <v>6</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5825,12 +5849,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5855,33 +5879,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 156,00</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 19,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5898,12 +5922,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5975,12 +5999,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6005,33 +6029,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 234,00</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,9%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>76</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 2,6%</t>
+        <v>0</v>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6048,12 +6072,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6125,12 +6149,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6155,33 +6179,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 467,00</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>▼ 27,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6198,12 +6222,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6275,12 +6299,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6305,33 +6329,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 545,00</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 74,7%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>107</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,3%</t>
+        <v>1</v>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6348,12 +6372,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6378,7 +6402,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6386,8 +6410,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" s="2" t="n">
-        <v>0</v>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6396,37 +6422,39 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6451,33 +6479,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 312,00</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>97</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 203,1%</t>
+        <v>0</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6494,12 +6522,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6524,7 +6552,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6532,8 +6560,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="n">
-        <v>0</v>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -6542,37 +6572,39 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6606,16 +6638,16 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1500,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
@@ -6623,12 +6655,12 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
@@ -6640,12 +6672,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6670,7 +6702,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6678,47 +6710,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6746,17 +6782,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6786,12 +6822,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6816,55 +6852,59 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J85" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6889,33 +6929,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 78,00</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 99,2%</t>
-        </is>
-      </c>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6932,12 +6972,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6962,7 +7002,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6970,8 +7010,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I87" s="2" t="n">
-        <v>2</v>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -6980,37 +7022,39 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7035,33 +7079,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 659,00</t>
-        </is>
-      </c>
-      <c r="H88" s="4" t="inlineStr">
-        <is>
-          <t>▲ 124,9%</t>
+          <t>R$ 312,00</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>▲ 4,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -7078,12 +7122,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7108,55 +7152,59 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7181,38 +7229,38 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 293,00</t>
-        </is>
-      </c>
-      <c r="H90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 390,00</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>115</v>
+        <v>62</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>▼ 12,2%</t>
+          <t>▼ 4,6%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
@@ -7224,12 +7272,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7254,7 +7302,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -7262,47 +7310,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I91" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,5%</t>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7327,20 +7379,20 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 439,00</t>
+          <t>R$ 234,00</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,1%</t>
+          <t>▼ 49,9%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>131</v>
+        <v>65</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>▼ 0,8%</t>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7349,11 +7401,11 @@
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7370,12 +7422,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7400,7 +7452,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7408,47 +7460,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I93" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J93" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7473,33 +7529,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 586,00</t>
-        </is>
-      </c>
-      <c r="H94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,1%</t>
+          <t>R$ 467,00</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>▲ 199,4%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>132</v>
+        <v>91</v>
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>▲ 34,7%</t>
+          <t>▲ 49,2%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7516,12 +7572,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7546,55 +7602,59 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H95" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I95" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J95" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7619,33 +7679,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 659,00</t>
-        </is>
-      </c>
-      <c r="H96" s="4" t="inlineStr">
-        <is>
-          <t>▲ 80,1%</t>
+          <t>R$ 156,00</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>98</v>
-      </c>
-      <c r="J96" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3,2%</t>
+        <v>61</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 19,7%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7662,12 +7722,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7692,7 +7752,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7700,47 +7760,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I97" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J97" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7765,33 +7829,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 366,00</t>
+          <t>R$ 234,00</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>▼ 61,6%</t>
+          <t>▼ 49,9%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>95</v>
-      </c>
-      <c r="J98" s="4" t="inlineStr">
-        <is>
-          <t>▲ 13,1%</t>
+        <v>76</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 2,6%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7808,12 +7872,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7838,7 +7902,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -7846,47 +7910,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I99" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>▼ 63,2%</t>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7911,33 +7979,33 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 952,00</t>
-        </is>
-      </c>
-      <c r="H100" s="4" t="inlineStr">
-        <is>
-          <t>▲ 210,1%</t>
+          <t>R$ 467,00</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>84</v>
-      </c>
-      <c r="J100" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1,2%</t>
+        <v>78</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 27,1%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7954,12 +8022,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7984,7 +8052,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -7992,47 +8060,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I101" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>▼ 26,9%</t>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L101" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8057,33 +8129,33 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 307,00</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 545,00</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>▲ 74,7%</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>107</v>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>▲ 10,3%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -8100,12 +8172,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8139,7 +8211,7 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
@@ -8170,8 +8242,1760 @@
         </is>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 312,00</t>
+        </is>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>▲ 203,1%</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>4,7%</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,00</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1500,0%</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>3,1%</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H109" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>▼ 99,2%</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>R$ 75,00</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 659,00</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t>▲ 124,9%</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>▲ 4,3%</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>7,5%</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>6,5%</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H113" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 293,00</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,2%</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>2,8%</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>R$ 75,00</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,5%</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>14,3%</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 439,00</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,1%</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 0,8%</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>4,6%</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 586,00</t>
+        </is>
+      </c>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,1%</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>132</v>
+      </c>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>▲ 34,7%</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>6,1%</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>6,8%</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H119" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J119" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 659,00</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t>▲ 80,1%</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3,2%</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>9,2%</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>6,3%</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>R$ 75,00</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J121" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 366,00</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 61,6%</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>▲ 13,1%</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>5,3%</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>▼ 63,2%</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 952,00</t>
+        </is>
+      </c>
+      <c r="H124" s="4" t="inlineStr">
+        <is>
+          <t>▲ 210,1%</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="J124" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1,2%</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>15,5%</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>11,3%</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>▼ 26,9%</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 307,00</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O103"/>
+  <autoFilter ref="A1:O127"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-019-VASSOURA-INFANTIL-UNICORNIO.xlsx
+++ b/saida_skus/SKU_BRINQ-019-VASSOURA-INFANTIL-UNICORNIO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O127"/>
+  <dimension ref="A1:O169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -751,10 +751,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -763,39 +761,37 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -867,12 +863,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -897,7 +893,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -905,8 +901,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -915,37 +913,39 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1017,12 +1017,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1094,12 +1094,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1171,12 +1171,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1209,10 +1209,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1221,39 +1219,37 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1325,12 +1321,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1402,12 +1398,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1479,12 +1475,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1509,7 +1505,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1517,8 +1513,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I14" s="2" t="n">
-        <v>0</v>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1527,37 +1525,39 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1667,8 +1667,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I16" s="2" t="n">
-        <v>0</v>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1677,37 +1679,39 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1779,12 +1783,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1809,7 +1813,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1817,8 +1821,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="2" t="n">
-        <v>0</v>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1827,37 +1833,39 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1929,12 +1937,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1959,7 +1967,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1967,8 +1975,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="2" t="n">
-        <v>0</v>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1977,37 +1987,39 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2079,12 +2091,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2156,12 +2168,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2233,12 +2245,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2263,7 +2275,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2271,8 +2283,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I24" s="2" t="n">
-        <v>0</v>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -2281,37 +2295,39 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2383,12 +2399,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2424,9 +2440,9 @@
       <c r="I26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2456,12 +2472,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2533,12 +2549,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2572,7 +2588,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -2606,12 +2622,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2683,12 +2699,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2724,9 +2740,9 @@
       <c r="I30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2756,12 +2772,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2833,12 +2849,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2872,7 +2888,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2906,12 +2922,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2983,12 +2999,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3013,7 +3029,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3021,8 +3037,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I34" s="2" t="n">
-        <v>0</v>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -3031,37 +3049,39 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3133,12 +3153,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3163,7 +3183,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3171,8 +3191,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I36" s="2" t="n">
-        <v>0</v>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -3181,37 +3203,39 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3283,12 +3307,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3313,7 +3337,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3321,8 +3345,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I38" s="2" t="n">
-        <v>0</v>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -3331,37 +3357,39 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3433,12 +3461,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3463,7 +3491,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3471,10 +3499,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I40" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -3483,39 +3509,37 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3587,12 +3611,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3617,7 +3641,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3625,8 +3649,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I42" s="2" t="n">
-        <v>0</v>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -3635,37 +3661,39 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3737,12 +3765,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3767,7 +3795,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3775,8 +3803,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I44" s="2" t="n">
-        <v>0</v>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -3785,37 +3815,39 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3887,12 +3919,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3917,7 +3949,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3925,8 +3957,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I46" s="2" t="n">
-        <v>0</v>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3935,37 +3969,39 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4037,12 +4073,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4067,7 +4103,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4075,10 +4111,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I48" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -4087,39 +4121,37 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4191,12 +4223,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4268,12 +4300,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4345,12 +4377,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4375,7 +4407,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4383,8 +4415,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I52" s="2" t="n">
-        <v>0</v>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4393,37 +4427,39 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4495,12 +4531,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4525,7 +4561,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4533,8 +4569,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I54" s="2" t="n">
-        <v>0</v>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -4543,37 +4581,39 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4645,12 +4685,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4718,12 +4758,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4795,12 +4835,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4836,9 +4876,9 @@
       <c r="I58" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4868,12 +4908,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4945,12 +4985,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4984,7 +5024,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -5018,12 +5058,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5095,12 +5135,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5136,9 +5176,9 @@
       <c r="I62" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5168,12 +5208,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5245,12 +5285,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5275,7 +5315,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5283,8 +5323,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I64" s="2" t="n">
-        <v>1</v>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5293,37 +5335,39 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5395,12 +5439,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5468,12 +5512,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5545,12 +5589,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5586,9 +5630,9 @@
       <c r="I68" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5618,12 +5662,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5695,12 +5739,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5725,7 +5769,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5733,10 +5777,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I70" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
@@ -5745,39 +5787,37 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5849,12 +5889,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5890,9 +5930,9 @@
       <c r="I72" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5922,12 +5962,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5999,12 +6039,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6038,7 +6078,7 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
@@ -6072,12 +6112,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6149,12 +6189,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6190,9 +6230,9 @@
       <c r="I76" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6222,12 +6262,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6299,12 +6339,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6338,7 +6378,7 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
@@ -6372,12 +6412,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6449,12 +6489,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6482,17 +6522,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6522,12 +6562,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6599,12 +6639,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6629,7 +6669,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6637,8 +6677,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I82" s="2" t="n">
-        <v>7</v>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
@@ -6647,37 +6689,39 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6749,12 +6793,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6782,17 +6826,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6822,12 +6866,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6899,12 +6943,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6929,16 +6973,16 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
-        </is>
-      </c>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
@@ -6947,15 +6991,15 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6972,12 +7016,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7049,12 +7093,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7079,20 +7123,20 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 312,00</t>
-        </is>
-      </c>
-      <c r="H88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -7101,11 +7145,11 @@
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -7122,12 +7166,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7199,12 +7243,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7229,55 +7273,59 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 390,00</t>
-        </is>
-      </c>
-      <c r="H90" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,6%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="n">
-        <v>5</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7349,12 +7397,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7379,55 +7427,59 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 234,00</t>
-        </is>
-      </c>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,9%</t>
-        </is>
-      </c>
-      <c r="I92" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 28,6%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
-        </is>
-      </c>
-      <c r="L92" s="2" t="n">
-        <v>3</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7499,12 +7551,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7529,33 +7581,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 467,00</t>
-        </is>
-      </c>
-      <c r="H94" s="4" t="inlineStr">
-        <is>
-          <t>▲ 199,4%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>▲ 49,2%</t>
+        <v>0</v>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7572,12 +7624,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7649,12 +7701,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7679,33 +7731,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 156,00</t>
-        </is>
-      </c>
-      <c r="H96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 19,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7722,12 +7774,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7799,12 +7851,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7829,33 +7881,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 234,00</t>
-        </is>
-      </c>
-      <c r="H98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,9%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>76</v>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 2,6%</t>
+        <v>0</v>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7872,12 +7924,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7949,12 +8001,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7979,33 +8031,33 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 467,00</t>
-        </is>
-      </c>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>▼ 27,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -8022,12 +8074,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8099,12 +8151,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8129,33 +8181,33 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 545,00</t>
-        </is>
-      </c>
-      <c r="H102" s="4" t="inlineStr">
-        <is>
-          <t>▲ 74,7%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>107</v>
-      </c>
-      <c r="J102" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,3%</t>
+        <v>1</v>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -8172,12 +8224,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8202,7 +8254,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -8210,8 +8262,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I103" s="2" t="n">
-        <v>0</v>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
@@ -8220,37 +8274,39 @@
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8275,33 +8331,33 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 312,00</t>
-        </is>
-      </c>
-      <c r="H104" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>97</v>
-      </c>
-      <c r="J104" s="4" t="inlineStr">
-        <is>
-          <t>▲ 203,1%</t>
+        <v>0</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -8318,12 +8374,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8348,7 +8404,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -8356,8 +8412,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I105" s="2" t="n">
-        <v>0</v>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
@@ -8366,37 +8424,39 @@
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L105" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8421,7 +8481,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -8430,29 +8490,29 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J106" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1500,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L106" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O106" s="2" t="inlineStr">
@@ -8464,12 +8524,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8494,7 +8554,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -8502,47 +8562,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J107" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L107" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8576,11 +8640,11 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J108" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8610,12 +8674,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8640,55 +8704,59 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H109" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I109" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J109" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L109" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8716,17 +8784,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H110" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J110" s="3" t="inlineStr">
-        <is>
-          <t>▼ 99,2%</t>
+        <v>0</v>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -8756,12 +8824,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8786,7 +8854,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -8794,8 +8862,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I111" s="2" t="n">
-        <v>2</v>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
@@ -8804,37 +8874,39 @@
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
-        </is>
-      </c>
-      <c r="L111" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8859,55 +8931,59 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 659,00</t>
-        </is>
-      </c>
-      <c r="H112" s="4" t="inlineStr">
-        <is>
-          <t>▲ 124,9%</t>
-        </is>
-      </c>
-      <c r="I112" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="J112" s="4" t="inlineStr">
-        <is>
-          <t>▲ 4,3%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
-        </is>
-      </c>
-      <c r="L112" s="2" t="n">
-        <v>9</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8932,55 +9008,59 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H113" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I113" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J113" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L113" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -9005,38 +9085,38 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 293,00</t>
-        </is>
-      </c>
-      <c r="H114" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>115</v>
-      </c>
-      <c r="J114" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,2%</t>
+        <v>0</v>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O114" s="2" t="inlineStr">
@@ -9048,12 +9128,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9078,7 +9158,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -9086,47 +9166,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I115" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J115" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,5%</t>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
-        </is>
-      </c>
-      <c r="L115" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9151,33 +9235,33 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 439,00</t>
-        </is>
-      </c>
-      <c r="H116" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>131</v>
-      </c>
-      <c r="J116" s="3" t="inlineStr">
-        <is>
-          <t>▼ 0,8%</t>
+        <v>0</v>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -9194,12 +9278,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9224,7 +9308,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -9232,47 +9316,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I117" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J117" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L117" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9297,33 +9385,33 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 586,00</t>
-        </is>
-      </c>
-      <c r="H118" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>132</v>
-      </c>
-      <c r="J118" s="4" t="inlineStr">
-        <is>
-          <t>▲ 34,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9340,12 +9428,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9370,55 +9458,59 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H119" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I119" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J119" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L119" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9443,33 +9535,33 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 659,00</t>
-        </is>
-      </c>
-      <c r="H120" s="4" t="inlineStr">
-        <is>
-          <t>▲ 80,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>98</v>
-      </c>
-      <c r="J120" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3,2%</t>
+        <v>1</v>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9486,12 +9578,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9516,7 +9608,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -9524,47 +9616,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I121" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J121" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
-        </is>
-      </c>
-      <c r="L121" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9589,33 +9685,33 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 366,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
-          <t>▼ 61,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>95</v>
-      </c>
-      <c r="J122" s="4" t="inlineStr">
-        <is>
-          <t>▲ 13,1%</t>
+        <v>0</v>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9632,12 +9728,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9662,7 +9758,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -9670,47 +9766,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I123" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J123" s="3" t="inlineStr">
-        <is>
-          <t>▼ 63,2%</t>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L123" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9735,33 +9835,33 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 952,00</t>
-        </is>
-      </c>
-      <c r="H124" s="4" t="inlineStr">
-        <is>
-          <t>▲ 210,1%</t>
+          <t>R$ 78,00</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>84</v>
-      </c>
-      <c r="J124" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1,2%</t>
+        <v>7</v>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9778,12 +9878,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9808,7 +9908,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -9816,47 +9916,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I125" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J125" s="3" t="inlineStr">
-        <is>
-          <t>▼ 26,9%</t>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L125" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9881,33 +9985,33 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 307,00</t>
-        </is>
-      </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="J126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L126" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -9924,78 +10028,3180 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,00</t>
+        </is>
+      </c>
+      <c r="H128" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>R$ 312,00</t>
+        </is>
+      </c>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>4,0%</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>R$ 390,00</t>
+        </is>
+      </c>
+      <c r="H132" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,6%</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>8,1%</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>5,2%</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>R$ 234,00</t>
+        </is>
+      </c>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,9%</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,6%</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>4,6%</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>R$ 467,00</t>
+        </is>
+      </c>
+      <c r="H136" s="4" t="inlineStr">
+        <is>
+          <t>▲ 199,4%</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="J136" s="4" t="inlineStr">
+        <is>
+          <t>▲ 49,2%</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>6,6%</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>4,7%</t>
+        </is>
+      </c>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>R$ 156,00</t>
+        </is>
+      </c>
+      <c r="H138" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>▼ 19,7%</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>R$ 234,00</t>
+        </is>
+      </c>
+      <c r="H140" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,9%</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>▼ 2,6%</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>3,9%</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>R$ 467,00</t>
+        </is>
+      </c>
+      <c r="H142" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>▼ 27,1%</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>4,3%</t>
+        </is>
+      </c>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>R$ 545,00</t>
+        </is>
+      </c>
+      <c r="H144" s="4" t="inlineStr">
+        <is>
+          <t>▲ 74,7%</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="J144" s="4" t="inlineStr">
+        <is>
+          <t>▲ 10,3%</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>6,5%</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>4,5%</t>
+        </is>
+      </c>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>R$ 312,00</t>
+        </is>
+      </c>
+      <c r="H146" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="J146" s="4" t="inlineStr">
+        <is>
+          <t>▲ 203,1%</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>4,7%</t>
+        </is>
+      </c>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,00</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="J148" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1500,0%</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>3,1%</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J150" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H151" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J151" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H152" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J152" s="3" t="inlineStr">
+        <is>
+          <t>▼ 99,2%</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>R$ 75,00</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>R$ 659,00</t>
+        </is>
+      </c>
+      <c r="H154" s="4" t="inlineStr">
+        <is>
+          <t>▲ 124,9%</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="J154" s="4" t="inlineStr">
+        <is>
+          <t>▲ 4,3%</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>7,5%</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>6,5%</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H155" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>R$ 293,00</t>
+        </is>
+      </c>
+      <c r="H156" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="J156" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,2%</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>2,8%</t>
+        </is>
+      </c>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>R$ 75,00</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J157" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,5%</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>14,3%</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>R$ 439,00</t>
+        </is>
+      </c>
+      <c r="H158" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,1%</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>▼ 0,8%</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>4,6%</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J159" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>R$ 586,00</t>
+        </is>
+      </c>
+      <c r="H160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,1%</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="n">
+        <v>132</v>
+      </c>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>▲ 34,7%</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>6,1%</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>6,8%</t>
+        </is>
+      </c>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H161" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J161" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>R$ 659,00</t>
+        </is>
+      </c>
+      <c r="H162" s="4" t="inlineStr">
+        <is>
+          <t>▲ 80,1%</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="J162" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3,2%</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>9,2%</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>6,3%</t>
+        </is>
+      </c>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>R$ 75,00</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J163" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>R$ 366,00</t>
+        </is>
+      </c>
+      <c r="H164" s="3" t="inlineStr">
+        <is>
+          <t>▼ 61,6%</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="J164" s="4" t="inlineStr">
+        <is>
+          <t>▲ 13,1%</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>5,3%</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J165" s="3" t="inlineStr">
+        <is>
+          <t>▼ 63,2%</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>R$ 952,00</t>
+        </is>
+      </c>
+      <c r="H166" s="4" t="inlineStr">
+        <is>
+          <t>▲ 210,1%</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="J166" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1,2%</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>15,5%</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>11,3%</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="J167" s="3" t="inlineStr">
+        <is>
+          <t>▼ 26,9%</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>BRINQ-019</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>Vassoura infantil unicornio</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>R$ 307,00</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>6311164080</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>R$ 78,80</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I127" s="2" t="n">
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="J127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K127" s="2" t="inlineStr">
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="L127" s="2" t="n">
+      <c r="L169" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M127" s="2" t="inlineStr">
+      <c r="M169" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="N127" s="2" t="inlineStr">
+      <c r="N169" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O127" s="2" t="inlineStr">
+      <c r="O169" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O127"/>
+  <autoFilter ref="A1:O169"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-019-VASSOURA-INFANTIL-UNICORNIO.xlsx
+++ b/saida_skus/SKU_BRINQ-019-VASSOURA-INFANTIL-UNICORNIO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O169"/>
+  <dimension ref="A1:O171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -713,14 +713,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -743,7 +743,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -751,8 +751,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n">
-        <v>0</v>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -761,37 +763,39 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -863,14 +867,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -893,7 +897,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -901,10 +905,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -913,39 +915,37 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1017,12 +1017,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1094,12 +1094,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1171,14 +1171,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1209,8 +1209,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="2" t="n">
-        <v>0</v>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1219,37 +1221,39 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1321,14 +1325,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -1351,7 +1355,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1359,10 +1363,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I12" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1371,39 +1373,37 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1475,12 +1475,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1552,12 +1552,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1706,12 +1706,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1783,12 +1783,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1860,12 +1860,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2014,12 +2014,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2091,12 +2091,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2322,12 +2322,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2399,14 +2399,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2437,8 +2437,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I26" s="2" t="n">
-        <v>0</v>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -2447,37 +2449,39 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2549,12 +2553,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2622,12 +2626,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2699,12 +2703,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2772,12 +2776,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2849,12 +2853,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2922,12 +2926,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2999,14 +3003,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -3029,7 +3033,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3037,10 +3041,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I34" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -3049,39 +3051,37 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3230,12 +3230,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3307,12 +3307,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3384,12 +3384,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3461,14 +3461,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3499,8 +3499,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I40" s="2" t="n">
-        <v>0</v>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -3509,37 +3511,39 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3611,14 +3615,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -3641,7 +3645,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3649,10 +3653,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I42" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -3661,39 +3663,37 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3842,12 +3842,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3919,12 +3919,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4073,14 +4073,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4111,8 +4111,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I48" s="2" t="n">
-        <v>0</v>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -4121,37 +4123,39 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4223,14 +4227,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -4253,7 +4257,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4261,10 +4265,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I50" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4273,39 +4275,37 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4377,12 +4377,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4454,12 +4454,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4685,14 +4685,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4723,8 +4723,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I56" s="2" t="n">
-        <v>0</v>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4733,37 +4735,39 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4835,12 +4839,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4908,12 +4912,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4985,12 +4989,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5058,12 +5062,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5135,12 +5139,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5208,12 +5212,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5285,14 +5289,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -5315,7 +5319,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5323,10 +5327,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I64" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5335,39 +5337,37 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5439,14 +5439,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -5469,7 +5469,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5477,8 +5477,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I66" s="2" t="n">
-        <v>0</v>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -5487,37 +5489,39 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5589,12 +5593,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5630,9 +5634,9 @@
       <c r="I68" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5662,12 +5666,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5739,14 +5743,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -5778,11 +5782,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5812,12 +5816,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5889,14 +5893,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -5928,11 +5932,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5962,12 +5966,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6039,14 +6043,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -6078,11 +6082,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -6112,12 +6116,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6189,14 +6193,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -6228,7 +6232,7 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
@@ -6262,12 +6266,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6339,12 +6343,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6412,12 +6416,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6489,12 +6493,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6562,12 +6566,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6639,14 +6643,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -6669,7 +6673,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6677,10 +6681,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I82" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
@@ -6689,39 +6691,37 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6793,14 +6793,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -6823,7 +6823,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -6831,8 +6831,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I84" s="2" t="n">
-        <v>0</v>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
@@ -6841,37 +6843,39 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6943,12 +6947,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -7016,12 +7020,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7093,12 +7097,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7166,12 +7170,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7243,14 +7247,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -7273,7 +7277,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -7281,10 +7285,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I90" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
@@ -7293,39 +7295,37 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7397,12 +7397,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7474,12 +7474,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7551,14 +7551,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -7581,7 +7581,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -7589,8 +7589,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I94" s="2" t="n">
-        <v>0</v>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
@@ -7599,37 +7601,39 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7701,12 +7705,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7774,12 +7778,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7851,12 +7855,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7924,12 +7928,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -8001,12 +8005,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -8042,9 +8046,9 @@
       <c r="I100" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -8074,12 +8078,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8151,14 +8155,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -8190,11 +8194,11 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -8224,12 +8228,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8301,14 +8305,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -8340,11 +8344,11 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8374,12 +8378,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8451,14 +8455,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -8490,11 +8494,11 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J106" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8524,12 +8528,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8601,14 +8605,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -8640,7 +8644,7 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
@@ -8674,12 +8678,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8751,12 +8755,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8824,12 +8828,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8901,14 +8905,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -8931,7 +8935,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -8939,10 +8943,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I112" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I112" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
@@ -8951,39 +8953,37 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L112" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -9055,14 +9055,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -9085,7 +9085,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -9093,8 +9093,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I114" s="2" t="n">
-        <v>0</v>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
@@ -9103,37 +9105,39 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L114" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9205,12 +9209,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9278,12 +9282,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9355,12 +9359,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9396,9 +9400,9 @@
       <c r="I118" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J118" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -9428,12 +9432,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9505,14 +9509,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -9544,11 +9548,11 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J120" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -9578,12 +9582,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9655,14 +9659,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -9688,17 +9692,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H122" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J122" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -9728,12 +9732,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9805,14 +9809,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -9835,33 +9839,33 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
-        </is>
-      </c>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J124" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9878,12 +9882,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9955,14 +9959,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -9985,33 +9989,33 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H126" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 78,00</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J126" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L126" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -10028,12 +10032,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -10105,14 +10109,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -10135,33 +10139,33 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H128" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J128" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -10178,12 +10182,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10255,14 +10259,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -10285,33 +10289,33 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 312,00</t>
+          <t>R$ 78,00</t>
         </is>
       </c>
       <c r="H130" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J130" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>15</v>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -10328,12 +10332,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10405,14 +10409,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -10435,33 +10439,33 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 390,00</t>
-        </is>
-      </c>
-      <c r="H132" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+          <t>R$ 312,00</t>
+        </is>
+      </c>
+      <c r="H132" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>▼ 4,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L132" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10478,12 +10482,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10555,14 +10559,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -10585,33 +10589,33 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>R$ 234,00</t>
-        </is>
-      </c>
-      <c r="H134" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,9%</t>
+          <t>R$ 390,00</t>
+        </is>
+      </c>
+      <c r="H134" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
-          <t>▼ 28,6%</t>
+          <t>▼ 4,6%</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="L134" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -10628,12 +10632,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10705,14 +10709,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -10735,33 +10739,33 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>R$ 467,00</t>
-        </is>
-      </c>
-      <c r="H136" s="4" t="inlineStr">
-        <is>
-          <t>▲ 199,4%</t>
+          <t>R$ 234,00</t>
+        </is>
+      </c>
+      <c r="H136" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,9%</t>
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="J136" s="4" t="inlineStr">
-        <is>
-          <t>▲ 49,2%</t>
+        <v>65</v>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L136" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -10778,12 +10782,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10855,14 +10859,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -10885,33 +10889,33 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>R$ 156,00</t>
-        </is>
-      </c>
-      <c r="H138" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 467,00</t>
+        </is>
+      </c>
+      <c r="H138" s="4" t="inlineStr">
+        <is>
+          <t>▲ 199,4%</t>
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="J138" s="3" t="inlineStr">
-        <is>
-          <t>▼ 19,7%</t>
+        <v>91</v>
+      </c>
+      <c r="J138" s="4" t="inlineStr">
+        <is>
+          <t>▲ 49,2%</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="L138" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -10928,12 +10932,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -11005,14 +11009,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -11035,33 +11039,33 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>R$ 234,00</t>
+          <t>R$ 156,00</t>
         </is>
       </c>
       <c r="H140" s="3" t="inlineStr">
         <is>
-          <t>▼ 49,9%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>▼ 2,6%</t>
+          <t>▼ 19,7%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L140" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -11078,12 +11082,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -11155,14 +11159,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -11185,33 +11189,33 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>R$ 467,00</t>
+          <t>R$ 234,00</t>
         </is>
       </c>
       <c r="H142" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 49,9%</t>
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>▼ 27,1%</t>
+          <t>▼ 2,6%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L142" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -11228,12 +11232,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11305,14 +11309,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -11335,33 +11339,33 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>R$ 545,00</t>
-        </is>
-      </c>
-      <c r="H144" s="4" t="inlineStr">
-        <is>
-          <t>▲ 74,7%</t>
+          <t>R$ 467,00</t>
+        </is>
+      </c>
+      <c r="H144" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>107</v>
-      </c>
-      <c r="J144" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,3%</t>
+        <v>78</v>
+      </c>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>▼ 27,1%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L144" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -11378,14 +11382,14 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -11408,7 +11412,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -11416,8 +11420,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I145" s="2" t="n">
-        <v>0</v>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
@@ -11426,39 +11432,41 @@
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L145" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -11481,33 +11489,33 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>R$ 312,00</t>
+          <t>R$ 545,00</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▲ 74,7%</t>
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="J146" s="4" t="inlineStr">
         <is>
-          <t>▲ 203,1%</t>
+          <t>▲ 10,3%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L146" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -11524,12 +11532,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11597,14 +11605,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -11627,38 +11635,38 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
-        </is>
-      </c>
-      <c r="H148" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 312,00</t>
+        </is>
+      </c>
+      <c r="H148" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="J148" s="4" t="inlineStr">
         <is>
-          <t>▲ 1500,0%</t>
+          <t>▲ 203,1%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L148" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O148" s="2" t="inlineStr">
@@ -11670,12 +11678,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11711,9 +11719,9 @@
       <c r="I149" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J149" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
@@ -11743,14 +11751,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -11773,7 +11781,7 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 78,00</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -11782,29 +11790,29 @@
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="J150" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 1500,0%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L150" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O150" s="2" t="inlineStr">
@@ -11816,14 +11824,14 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -11849,17 +11857,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H151" s="3" t="inlineStr">
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I151" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J151" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
@@ -11889,14 +11897,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -11922,17 +11930,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H152" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J152" s="3" t="inlineStr">
-        <is>
-          <t>▼ 99,2%</t>
+        <v>2</v>
+      </c>
+      <c r="J152" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -11962,14 +11970,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -11992,33 +12000,33 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
-        </is>
-      </c>
-      <c r="H153" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H153" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J153" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J153" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L153" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
@@ -12035,14 +12043,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -12065,33 +12073,33 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 659,00</t>
-        </is>
-      </c>
-      <c r="H154" s="4" t="inlineStr">
-        <is>
-          <t>▲ 124,9%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="J154" s="4" t="inlineStr">
-        <is>
-          <t>▲ 4,3%</t>
+        <v>1</v>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 99,2%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -12108,14 +12116,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -12138,33 +12146,33 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H155" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 75,00</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J155" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L155" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
@@ -12181,14 +12189,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -12211,38 +12219,38 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 293,00</t>
-        </is>
-      </c>
-      <c r="H156" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 659,00</t>
+        </is>
+      </c>
+      <c r="H156" s="4" t="inlineStr">
+        <is>
+          <t>▲ 124,9%</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>115</v>
-      </c>
-      <c r="J156" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,2%</t>
+        <v>120</v>
+      </c>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
+          <t>▲ 4,3%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="L156" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O156" s="2" t="inlineStr">
@@ -12254,14 +12262,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -12284,33 +12292,33 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
-        </is>
-      </c>
-      <c r="H157" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H157" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
-          <t>▼ 12,5%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L157" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
@@ -12327,14 +12335,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -12357,38 +12365,38 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 439,00</t>
+          <t>R$ 293,00</t>
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,1%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
-          <t>▼ 0,8%</t>
+          <t>▼ 12,2%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O158" s="2" t="inlineStr">
@@ -12400,14 +12408,14 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -12430,7 +12438,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 75,00</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -12439,24 +12447,24 @@
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L159" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
@@ -12473,14 +12481,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -12503,33 +12511,33 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 586,00</t>
+          <t>R$ 439,00</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>▼ 11,1%</t>
+          <t>▼ 25,1%</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>132</v>
-      </c>
-      <c r="J160" s="4" t="inlineStr">
-        <is>
-          <t>▲ 34,7%</t>
+        <v>131</v>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 0,8%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12546,14 +12554,14 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -12579,17 +12587,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H161" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J161" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J161" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -12619,14 +12627,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -12649,33 +12657,33 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 659,00</t>
-        </is>
-      </c>
-      <c r="H162" s="4" t="inlineStr">
-        <is>
-          <t>▲ 80,1%</t>
+          <t>R$ 586,00</t>
+        </is>
+      </c>
+      <c r="H162" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="J162" s="4" t="inlineStr">
         <is>
-          <t>▲ 3,2%</t>
+          <t>▲ 34,7%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12692,14 +12700,14 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -12722,33 +12730,33 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
-        </is>
-      </c>
-      <c r="H163" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H163" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J163" s="4" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L163" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N163" s="2" t="inlineStr">
@@ -12765,14 +12773,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -12795,33 +12803,33 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 366,00</t>
-        </is>
-      </c>
-      <c r="H164" s="3" t="inlineStr">
-        <is>
-          <t>▼ 61,6%</t>
+          <t>R$ 659,00</t>
+        </is>
+      </c>
+      <c r="H164" s="4" t="inlineStr">
+        <is>
+          <t>▲ 80,1%</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J164" s="4" t="inlineStr">
         <is>
-          <t>▲ 13,1%</t>
+          <t>▲ 3,2%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12838,14 +12846,14 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -12868,7 +12876,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 75,00</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -12877,24 +12885,24 @@
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J165" s="3" t="inlineStr">
-        <is>
-          <t>▼ 63,2%</t>
+        <v>8</v>
+      </c>
+      <c r="J165" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L165" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M165" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N165" s="2" t="inlineStr">
@@ -12911,14 +12919,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -12941,33 +12949,33 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 952,00</t>
-        </is>
-      </c>
-      <c r="H166" s="4" t="inlineStr">
-        <is>
-          <t>▲ 210,1%</t>
+          <t>R$ 366,00</t>
+        </is>
+      </c>
+      <c r="H166" s="3" t="inlineStr">
+        <is>
+          <t>▼ 61,6%</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J166" s="4" t="inlineStr">
         <is>
-          <t>▲ 1,2%</t>
+          <t>▲ 13,1%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12984,14 +12992,14 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -13023,11 +13031,11 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
-          <t>▼ 26,9%</t>
+          <t>▼ 63,2%</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -13057,14 +13065,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -13087,33 +13095,33 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>R$ 307,00</t>
-        </is>
-      </c>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 952,00</t>
+        </is>
+      </c>
+      <c r="H168" s="4" t="inlineStr">
+        <is>
+          <t>▲ 210,1%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="J168" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>84</v>
+      </c>
+      <c r="J168" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1,2%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="L168" s="2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -13130,14 +13138,14 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -13169,11 +13177,11 @@
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>19</v>
+      </c>
+      <c r="J169" s="3" t="inlineStr">
+        <is>
+          <t>▼ 26,9%</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -13200,8 +13208,154 @@
         </is>
       </c>
     </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 307,00</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O169"/>
+  <autoFilter ref="A1:O171"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-019-VASSOURA-INFANTIL-UNICORNIO.xlsx
+++ b/saida_skus/SKU_BRINQ-019-VASSOURA-INFANTIL-UNICORNIO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O171"/>
+  <dimension ref="A1:O173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -867,14 +867,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -897,7 +897,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -905,8 +905,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -915,37 +917,39 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1017,14 +1021,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -1047,7 +1051,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1055,10 +1059,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1067,39 +1069,37 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1171,12 +1171,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1248,12 +1248,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1325,14 +1325,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1363,8 +1363,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="2" t="n">
-        <v>0</v>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1373,37 +1375,39 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1475,14 +1479,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -1505,7 +1509,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1513,10 +1517,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I14" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1525,39 +1527,37 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1706,12 +1706,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1783,12 +1783,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1860,12 +1860,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2014,12 +2014,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2091,12 +2091,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2322,12 +2322,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2399,12 +2399,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2476,12 +2476,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2553,14 +2553,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2591,8 +2591,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I28" s="2" t="n">
-        <v>0</v>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -2601,37 +2603,39 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2703,12 +2707,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2776,12 +2780,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2853,12 +2857,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2926,12 +2930,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3003,12 +3007,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3076,12 +3080,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3153,14 +3157,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -3183,7 +3187,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3191,10 +3195,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I36" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -3203,39 +3205,37 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3307,12 +3307,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3384,12 +3384,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3461,12 +3461,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3615,14 +3615,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -3645,7 +3645,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3653,8 +3653,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I42" s="2" t="n">
-        <v>0</v>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -3663,37 +3665,39 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3765,14 +3769,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -3795,7 +3799,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3803,10 +3807,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I44" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -3815,39 +3817,37 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3919,12 +3919,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4150,12 +4150,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4227,14 +4227,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4265,8 +4265,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="2" t="n">
-        <v>0</v>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4275,37 +4277,39 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4377,14 +4381,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -4407,7 +4411,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4415,10 +4419,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I52" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4427,39 +4429,37 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4839,14 +4839,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4877,8 +4877,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I58" s="2" t="n">
-        <v>0</v>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4887,37 +4889,39 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4989,12 +4993,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5062,12 +5066,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5139,12 +5143,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5212,12 +5216,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5289,12 +5293,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5362,12 +5366,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5439,14 +5443,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -5469,7 +5473,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5477,10 +5481,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I66" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -5489,39 +5491,37 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5593,14 +5593,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5631,8 +5631,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I68" s="2" t="n">
-        <v>0</v>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5641,37 +5643,39 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5743,12 +5747,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5784,9 +5788,9 @@
       <c r="I70" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5816,12 +5820,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5893,14 +5897,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -5932,11 +5936,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5966,12 +5970,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6043,14 +6047,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -6082,11 +6086,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -6116,12 +6120,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6193,14 +6197,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -6232,11 +6236,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6266,12 +6270,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6343,14 +6347,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -6382,7 +6386,7 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
@@ -6416,12 +6420,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6493,12 +6497,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6566,12 +6570,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6643,12 +6647,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6716,12 +6720,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6793,14 +6797,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -6823,7 +6827,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -6831,10 +6835,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I84" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
@@ -6843,39 +6845,37 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6947,14 +6947,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -6977,7 +6977,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -6985,8 +6985,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I86" s="2" t="n">
-        <v>0</v>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
@@ -6995,37 +6997,39 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7097,12 +7101,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7170,12 +7174,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7247,12 +7251,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7320,12 +7324,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7397,14 +7401,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -7427,7 +7431,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -7435,10 +7439,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I92" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
@@ -7447,39 +7449,37 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7551,12 +7551,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7705,14 +7705,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -7735,7 +7735,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -7743,8 +7743,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I96" s="2" t="n">
-        <v>0</v>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
@@ -7753,37 +7755,39 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7855,12 +7859,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7928,12 +7932,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -8005,12 +8009,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -8078,12 +8082,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8155,12 +8159,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8196,9 +8200,9 @@
       <c r="I102" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -8228,12 +8232,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8305,14 +8309,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -8344,11 +8348,11 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8378,12 +8382,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8455,14 +8459,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -8494,11 +8498,11 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8528,12 +8532,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8605,14 +8609,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -8644,11 +8648,11 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J108" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8678,12 +8682,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8755,14 +8759,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -8794,7 +8798,7 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
@@ -8828,12 +8832,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8905,12 +8909,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8978,12 +8982,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -9055,14 +9059,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -9085,7 +9089,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -9093,10 +9097,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I114" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
@@ -9105,39 +9107,37 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9209,14 +9209,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -9239,7 +9239,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -9247,8 +9247,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I116" s="2" t="n">
-        <v>0</v>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
@@ -9257,37 +9259,39 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L116" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9359,12 +9363,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9432,12 +9436,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9509,12 +9513,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9550,9 +9554,9 @@
       <c r="I120" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J120" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -9582,12 +9586,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9659,14 +9663,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -9698,11 +9702,11 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J122" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -9732,12 +9736,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9809,14 +9813,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -9842,17 +9846,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H124" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J124" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9882,12 +9886,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9959,14 +9963,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -9989,33 +9993,33 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
-        </is>
-      </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L126" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -10032,12 +10036,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -10109,14 +10113,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -10139,33 +10143,33 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H128" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 78,00</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J128" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -10182,12 +10186,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10259,14 +10263,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -10289,33 +10293,33 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H130" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J130" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -10332,12 +10336,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10409,14 +10413,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -10439,33 +10443,33 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 312,00</t>
+          <t>R$ 78,00</t>
         </is>
       </c>
       <c r="H132" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J132" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>15</v>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L132" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10482,12 +10486,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10559,14 +10563,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -10589,33 +10593,33 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>R$ 390,00</t>
-        </is>
-      </c>
-      <c r="H134" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+          <t>R$ 312,00</t>
+        </is>
+      </c>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
-          <t>▼ 4,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L134" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -10632,12 +10636,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10709,14 +10713,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -10739,33 +10743,33 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>R$ 234,00</t>
-        </is>
-      </c>
-      <c r="H136" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,9%</t>
+          <t>R$ 390,00</t>
+        </is>
+      </c>
+      <c r="H136" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
-          <t>▼ 28,6%</t>
+          <t>▼ 4,6%</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="L136" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -10782,12 +10786,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10859,14 +10863,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -10889,33 +10893,33 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>R$ 467,00</t>
-        </is>
-      </c>
-      <c r="H138" s="4" t="inlineStr">
-        <is>
-          <t>▲ 199,4%</t>
+          <t>R$ 234,00</t>
+        </is>
+      </c>
+      <c r="H138" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,9%</t>
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="J138" s="4" t="inlineStr">
-        <is>
-          <t>▲ 49,2%</t>
+        <v>65</v>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L138" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -10932,12 +10936,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -11009,14 +11013,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -11039,33 +11043,33 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>R$ 156,00</t>
-        </is>
-      </c>
-      <c r="H140" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 467,00</t>
+        </is>
+      </c>
+      <c r="H140" s="4" t="inlineStr">
+        <is>
+          <t>▲ 199,4%</t>
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="J140" s="3" t="inlineStr">
-        <is>
-          <t>▼ 19,7%</t>
+        <v>91</v>
+      </c>
+      <c r="J140" s="4" t="inlineStr">
+        <is>
+          <t>▲ 49,2%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="L140" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -11082,12 +11086,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -11159,14 +11163,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -11189,33 +11193,33 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>R$ 234,00</t>
+          <t>R$ 156,00</t>
         </is>
       </c>
       <c r="H142" s="3" t="inlineStr">
         <is>
-          <t>▼ 49,9%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>▼ 2,6%</t>
+          <t>▼ 19,7%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L142" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -11232,12 +11236,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11309,14 +11313,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -11339,33 +11343,33 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>R$ 467,00</t>
+          <t>R$ 234,00</t>
         </is>
       </c>
       <c r="H144" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 49,9%</t>
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
-          <t>▼ 27,1%</t>
+          <t>▼ 2,6%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L144" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -11382,12 +11386,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11459,14 +11463,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -11489,33 +11493,33 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>R$ 545,00</t>
-        </is>
-      </c>
-      <c r="H146" s="4" t="inlineStr">
-        <is>
-          <t>▲ 74,7%</t>
+          <t>R$ 467,00</t>
+        </is>
+      </c>
+      <c r="H146" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>107</v>
-      </c>
-      <c r="J146" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,3%</t>
+        <v>78</v>
+      </c>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
+          <t>▼ 27,1%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L146" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -11532,14 +11536,14 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -11562,7 +11566,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -11570,8 +11574,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I147" s="2" t="n">
-        <v>0</v>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
@@ -11580,39 +11586,41 @@
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L147" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N147" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -11635,33 +11643,33 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>R$ 312,00</t>
+          <t>R$ 545,00</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▲ 74,7%</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="J148" s="4" t="inlineStr">
         <is>
-          <t>▲ 203,1%</t>
+          <t>▲ 10,3%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L148" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -11678,12 +11686,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11751,14 +11759,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -11781,38 +11789,38 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
-        </is>
-      </c>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 312,00</t>
+        </is>
+      </c>
+      <c r="H150" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="J150" s="4" t="inlineStr">
         <is>
-          <t>▲ 1500,0%</t>
+          <t>▲ 203,1%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L150" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O150" s="2" t="inlineStr">
@@ -11824,12 +11832,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11865,9 +11873,9 @@
       <c r="I151" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J151" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
@@ -11897,14 +11905,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -11927,7 +11935,7 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 78,00</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -11936,29 +11944,29 @@
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="J152" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 1500,0%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L152" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O152" s="2" t="inlineStr">
@@ -11970,14 +11978,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -12003,17 +12011,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H153" s="3" t="inlineStr">
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I153" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J153" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -12043,14 +12051,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -12076,17 +12084,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H154" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J154" s="3" t="inlineStr">
-        <is>
-          <t>▼ 99,2%</t>
+        <v>2</v>
+      </c>
+      <c r="J154" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -12116,14 +12124,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -12146,33 +12154,33 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
-        </is>
-      </c>
-      <c r="H155" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H155" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J155" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J155" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L155" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
@@ -12189,14 +12197,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -12219,33 +12227,33 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 659,00</t>
-        </is>
-      </c>
-      <c r="H156" s="4" t="inlineStr">
-        <is>
-          <t>▲ 124,9%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H156" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="J156" s="4" t="inlineStr">
-        <is>
-          <t>▲ 4,3%</t>
+        <v>1</v>
+      </c>
+      <c r="J156" s="3" t="inlineStr">
+        <is>
+          <t>▼ 99,2%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L156" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -12262,14 +12270,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -12292,33 +12300,33 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H157" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 75,00</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J157" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L157" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
@@ -12335,14 +12343,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -12365,38 +12373,38 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 293,00</t>
-        </is>
-      </c>
-      <c r="H158" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 659,00</t>
+        </is>
+      </c>
+      <c r="H158" s="4" t="inlineStr">
+        <is>
+          <t>▲ 124,9%</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>115</v>
-      </c>
-      <c r="J158" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,2%</t>
+        <v>120</v>
+      </c>
+      <c r="J158" s="4" t="inlineStr">
+        <is>
+          <t>▲ 4,3%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O158" s="2" t="inlineStr">
@@ -12408,14 +12416,14 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -12438,33 +12446,33 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
-        </is>
-      </c>
-      <c r="H159" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H159" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
-          <t>▼ 12,5%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L159" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
@@ -12481,14 +12489,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -12511,38 +12519,38 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 439,00</t>
+          <t>R$ 293,00</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,1%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>▼ 0,8%</t>
+          <t>▼ 12,2%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O160" s="2" t="inlineStr">
@@ -12554,14 +12562,14 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -12584,7 +12592,7 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 75,00</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
@@ -12593,24 +12601,24 @@
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L161" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N161" s="2" t="inlineStr">
@@ -12627,14 +12635,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -12657,33 +12665,33 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 586,00</t>
+          <t>R$ 439,00</t>
         </is>
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>▼ 11,1%</t>
+          <t>▼ 25,1%</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>132</v>
-      </c>
-      <c r="J162" s="4" t="inlineStr">
-        <is>
-          <t>▲ 34,7%</t>
+        <v>131</v>
+      </c>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>▼ 0,8%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12700,14 +12708,14 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -12733,17 +12741,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H163" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J163" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J163" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -12773,14 +12781,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -12803,33 +12811,33 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 659,00</t>
-        </is>
-      </c>
-      <c r="H164" s="4" t="inlineStr">
-        <is>
-          <t>▲ 80,1%</t>
+          <t>R$ 586,00</t>
+        </is>
+      </c>
+      <c r="H164" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="J164" s="4" t="inlineStr">
         <is>
-          <t>▲ 3,2%</t>
+          <t>▲ 34,7%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12846,14 +12854,14 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -12876,33 +12884,33 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
-        </is>
-      </c>
-      <c r="H165" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H165" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J165" s="4" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L165" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M165" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N165" s="2" t="inlineStr">
@@ -12919,14 +12927,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -12949,33 +12957,33 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 366,00</t>
-        </is>
-      </c>
-      <c r="H166" s="3" t="inlineStr">
-        <is>
-          <t>▼ 61,6%</t>
+          <t>R$ 659,00</t>
+        </is>
+      </c>
+      <c r="H166" s="4" t="inlineStr">
+        <is>
+          <t>▲ 80,1%</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J166" s="4" t="inlineStr">
         <is>
-          <t>▲ 13,1%</t>
+          <t>▲ 3,2%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12992,14 +13000,14 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -13022,7 +13030,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 75,00</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -13031,24 +13039,24 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J167" s="3" t="inlineStr">
-        <is>
-          <t>▼ 63,2%</t>
+        <v>8</v>
+      </c>
+      <c r="J167" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L167" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N167" s="2" t="inlineStr">
@@ -13065,14 +13073,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -13095,33 +13103,33 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>R$ 952,00</t>
-        </is>
-      </c>
-      <c r="H168" s="4" t="inlineStr">
-        <is>
-          <t>▲ 210,1%</t>
+          <t>R$ 366,00</t>
+        </is>
+      </c>
+      <c r="H168" s="3" t="inlineStr">
+        <is>
+          <t>▼ 61,6%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J168" s="4" t="inlineStr">
         <is>
-          <t>▲ 1,2%</t>
+          <t>▲ 13,1%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L168" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -13138,14 +13146,14 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -13177,11 +13185,11 @@
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
-          <t>▼ 26,9%</t>
+          <t>▼ 63,2%</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -13211,14 +13219,14 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -13241,33 +13249,33 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>R$ 307,00</t>
-        </is>
-      </c>
-      <c r="H170" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 952,00</t>
+        </is>
+      </c>
+      <c r="H170" s="4" t="inlineStr">
+        <is>
+          <t>▲ 210,1%</t>
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="J170" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>84</v>
+      </c>
+      <c r="J170" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1,2%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="L170" s="2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -13284,14 +13292,14 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -13323,11 +13331,11 @@
         </is>
       </c>
       <c r="I171" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>19</v>
+      </c>
+      <c r="J171" s="3" t="inlineStr">
+        <is>
+          <t>▼ 26,9%</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
@@ -13354,8 +13362,154 @@
         </is>
       </c>
     </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 307,00</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O171"/>
+  <autoFilter ref="A1:O173"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-019-VASSOURA-INFANTIL-UNICORNIO.xlsx
+++ b/saida_skus/SKU_BRINQ-019-VASSOURA-INFANTIL-UNICORNIO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O173"/>
+  <dimension ref="A1:O175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -867,12 +867,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1021,14 +1021,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1059,8 +1059,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I8" s="2" t="n">
-        <v>0</v>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1069,37 +1071,39 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1171,14 +1175,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -1201,7 +1205,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1209,10 +1213,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1221,39 +1223,37 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1325,12 +1325,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1402,12 +1402,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1479,14 +1479,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1517,8 +1517,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I14" s="2" t="n">
-        <v>0</v>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1527,37 +1529,39 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1629,14 +1633,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -1659,7 +1663,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1667,10 +1671,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I16" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1679,39 +1681,37 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1783,12 +1783,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1860,12 +1860,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2014,12 +2014,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2091,12 +2091,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2322,12 +2322,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2399,12 +2399,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2476,12 +2476,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2553,12 +2553,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2707,14 +2707,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2745,8 +2745,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I30" s="2" t="n">
-        <v>0</v>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -2755,37 +2757,39 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2857,12 +2861,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2930,12 +2934,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3007,12 +3011,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3080,12 +3084,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3157,12 +3161,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3230,12 +3234,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3307,14 +3311,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -3337,7 +3341,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3345,10 +3349,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I38" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -3357,39 +3359,37 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3461,12 +3461,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3615,12 +3615,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3692,12 +3692,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3769,14 +3769,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3807,8 +3807,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I44" s="2" t="n">
-        <v>0</v>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -3817,37 +3819,39 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3919,14 +3923,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -3949,7 +3953,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3957,10 +3961,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I46" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3969,39 +3971,37 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4150,12 +4150,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4381,14 +4381,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4419,8 +4419,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I52" s="2" t="n">
-        <v>0</v>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4429,37 +4431,39 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4531,14 +4535,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -4561,7 +4565,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4569,10 +4573,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I54" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -4581,39 +4583,37 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4916,12 +4916,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4993,14 +4993,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -5031,8 +5031,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I60" s="2" t="n">
-        <v>0</v>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -5041,37 +5043,39 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5143,12 +5147,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5216,12 +5220,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5293,12 +5297,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5366,12 +5370,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5443,12 +5447,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5516,12 +5520,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5593,14 +5597,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -5623,7 +5627,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5631,10 +5635,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I68" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5643,39 +5645,37 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5747,14 +5747,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5785,8 +5785,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I70" s="2" t="n">
-        <v>0</v>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
@@ -5795,37 +5797,39 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5897,12 +5901,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5938,9 +5942,9 @@
       <c r="I72" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5970,12 +5974,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6047,14 +6051,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -6086,11 +6090,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -6120,12 +6124,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6197,14 +6201,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -6236,11 +6240,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6270,12 +6274,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6347,14 +6351,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -6386,11 +6390,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6420,12 +6424,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6497,14 +6501,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -6536,7 +6540,7 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
@@ -6570,12 +6574,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6647,12 +6651,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6720,12 +6724,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6797,12 +6801,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6870,12 +6874,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6947,14 +6951,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -6977,7 +6981,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -6985,10 +6989,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I86" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
@@ -6997,39 +6999,37 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7101,14 +7101,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -7131,7 +7131,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -7139,8 +7139,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I88" s="2" t="n">
-        <v>0</v>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
@@ -7149,37 +7151,39 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7251,12 +7255,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7324,12 +7328,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7401,12 +7405,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7474,12 +7478,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7551,14 +7555,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -7581,7 +7585,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -7589,10 +7593,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I94" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
@@ -7601,39 +7603,37 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7705,12 +7705,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7782,12 +7782,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7859,14 +7859,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -7889,7 +7889,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -7897,8 +7897,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I98" s="2" t="n">
-        <v>0</v>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
@@ -7907,37 +7909,39 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L98" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -8009,12 +8013,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -8082,12 +8086,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8159,12 +8163,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8232,12 +8236,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8309,12 +8313,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8350,9 +8354,9 @@
       <c r="I104" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8382,12 +8386,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8459,14 +8463,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -8498,11 +8502,11 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J106" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8532,12 +8536,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8609,14 +8613,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -8648,11 +8652,11 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J108" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8682,12 +8686,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8759,14 +8763,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -8798,11 +8802,11 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J110" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -8832,12 +8836,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8909,14 +8913,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -8948,7 +8952,7 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
@@ -8982,12 +8986,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -9059,12 +9063,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -9132,12 +9136,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9209,14 +9213,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -9239,7 +9243,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -9247,10 +9251,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I116" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I116" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
@@ -9259,39 +9261,37 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L116" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9363,14 +9363,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -9393,7 +9393,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -9401,8 +9401,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I118" s="2" t="n">
-        <v>0</v>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
@@ -9411,37 +9413,39 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L118" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9513,12 +9517,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9586,12 +9590,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9663,12 +9667,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9704,9 +9708,9 @@
       <c r="I122" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J122" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -9736,12 +9740,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9813,14 +9817,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -9852,11 +9856,11 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J124" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9886,12 +9890,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9963,14 +9967,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -9996,17 +10000,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H126" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J126" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -10036,12 +10040,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -10113,14 +10117,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -10143,33 +10147,33 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
-        </is>
-      </c>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H128" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J128" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -10186,12 +10190,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10263,14 +10267,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -10293,33 +10297,33 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H130" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 78,00</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J130" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -10336,12 +10340,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10413,14 +10417,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -10443,33 +10447,33 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H132" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J132" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L132" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10486,12 +10490,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10563,14 +10567,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -10593,33 +10597,33 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>R$ 312,00</t>
+          <t>R$ 78,00</t>
         </is>
       </c>
       <c r="H134" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J134" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>15</v>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L134" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -10636,12 +10640,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10713,14 +10717,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -10743,33 +10747,33 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>R$ 390,00</t>
-        </is>
-      </c>
-      <c r="H136" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+          <t>R$ 312,00</t>
+        </is>
+      </c>
+      <c r="H136" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
-          <t>▼ 4,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L136" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -10786,12 +10790,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10863,14 +10867,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -10893,33 +10897,33 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>R$ 234,00</t>
-        </is>
-      </c>
-      <c r="H138" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,9%</t>
+          <t>R$ 390,00</t>
+        </is>
+      </c>
+      <c r="H138" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
-          <t>▼ 28,6%</t>
+          <t>▼ 4,6%</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="L138" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -10936,12 +10940,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -11013,14 +11017,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -11043,33 +11047,33 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>R$ 467,00</t>
-        </is>
-      </c>
-      <c r="H140" s="4" t="inlineStr">
-        <is>
-          <t>▲ 199,4%</t>
+          <t>R$ 234,00</t>
+        </is>
+      </c>
+      <c r="H140" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,9%</t>
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="J140" s="4" t="inlineStr">
-        <is>
-          <t>▲ 49,2%</t>
+        <v>65</v>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L140" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -11086,12 +11090,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -11163,14 +11167,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -11193,33 +11197,33 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>R$ 156,00</t>
-        </is>
-      </c>
-      <c r="H142" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 467,00</t>
+        </is>
+      </c>
+      <c r="H142" s="4" t="inlineStr">
+        <is>
+          <t>▲ 199,4%</t>
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="J142" s="3" t="inlineStr">
-        <is>
-          <t>▼ 19,7%</t>
+        <v>91</v>
+      </c>
+      <c r="J142" s="4" t="inlineStr">
+        <is>
+          <t>▲ 49,2%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="L142" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -11236,12 +11240,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11313,14 +11317,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -11343,33 +11347,33 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>R$ 234,00</t>
+          <t>R$ 156,00</t>
         </is>
       </c>
       <c r="H144" s="3" t="inlineStr">
         <is>
-          <t>▼ 49,9%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
-          <t>▼ 2,6%</t>
+          <t>▼ 19,7%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L144" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -11386,12 +11390,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11463,14 +11467,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -11493,33 +11497,33 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>R$ 467,00</t>
+          <t>R$ 234,00</t>
         </is>
       </c>
       <c r="H146" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 49,9%</t>
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
-          <t>▼ 27,1%</t>
+          <t>▼ 2,6%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L146" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -11536,12 +11540,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11613,14 +11617,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -11643,33 +11647,33 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>R$ 545,00</t>
-        </is>
-      </c>
-      <c r="H148" s="4" t="inlineStr">
-        <is>
-          <t>▲ 74,7%</t>
+          <t>R$ 467,00</t>
+        </is>
+      </c>
+      <c r="H148" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>107</v>
-      </c>
-      <c r="J148" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,3%</t>
+        <v>78</v>
+      </c>
+      <c r="J148" s="3" t="inlineStr">
+        <is>
+          <t>▼ 27,1%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L148" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -11686,14 +11690,14 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -11716,7 +11720,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -11724,8 +11728,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I149" s="2" t="n">
-        <v>0</v>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
@@ -11734,39 +11740,41 @@
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L149" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -11789,33 +11797,33 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>R$ 312,00</t>
+          <t>R$ 545,00</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▲ 74,7%</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="J150" s="4" t="inlineStr">
         <is>
-          <t>▲ 203,1%</t>
+          <t>▲ 10,3%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L150" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -11832,12 +11840,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11905,14 +11913,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -11935,38 +11943,38 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
-        </is>
-      </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 312,00</t>
+        </is>
+      </c>
+      <c r="H152" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="J152" s="4" t="inlineStr">
         <is>
-          <t>▲ 1500,0%</t>
+          <t>▲ 203,1%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L152" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O152" s="2" t="inlineStr">
@@ -11978,12 +11986,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -12019,9 +12027,9 @@
       <c r="I153" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J153" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -12051,14 +12059,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -12081,7 +12089,7 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 78,00</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -12090,29 +12098,29 @@
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="J154" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 1500,0%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O154" s="2" t="inlineStr">
@@ -12124,14 +12132,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -12157,17 +12165,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H155" s="3" t="inlineStr">
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I155" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J155" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -12197,14 +12205,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -12230,17 +12238,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H156" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J156" s="3" t="inlineStr">
-        <is>
-          <t>▼ 99,2%</t>
+        <v>2</v>
+      </c>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -12270,14 +12278,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -12300,33 +12308,33 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
-        </is>
-      </c>
-      <c r="H157" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H157" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J157" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J157" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L157" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
@@ -12343,14 +12351,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -12373,33 +12381,33 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 659,00</t>
-        </is>
-      </c>
-      <c r="H158" s="4" t="inlineStr">
-        <is>
-          <t>▲ 124,9%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H158" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="J158" s="4" t="inlineStr">
-        <is>
-          <t>▲ 4,3%</t>
+        <v>1</v>
+      </c>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>▼ 99,2%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12416,14 +12424,14 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -12446,33 +12454,33 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H159" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 75,00</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J159" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L159" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
@@ -12489,14 +12497,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -12519,38 +12527,38 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 293,00</t>
-        </is>
-      </c>
-      <c r="H160" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 659,00</t>
+        </is>
+      </c>
+      <c r="H160" s="4" t="inlineStr">
+        <is>
+          <t>▲ 124,9%</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>115</v>
-      </c>
-      <c r="J160" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,2%</t>
+        <v>120</v>
+      </c>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>▲ 4,3%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O160" s="2" t="inlineStr">
@@ -12562,14 +12570,14 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -12592,33 +12600,33 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
-        </is>
-      </c>
-      <c r="H161" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H161" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
-          <t>▼ 12,5%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L161" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N161" s="2" t="inlineStr">
@@ -12635,14 +12643,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -12665,38 +12673,38 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 439,00</t>
+          <t>R$ 293,00</t>
         </is>
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,1%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
-          <t>▼ 0,8%</t>
+          <t>▼ 12,2%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O162" s="2" t="inlineStr">
@@ -12708,14 +12716,14 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -12738,7 +12746,7 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 75,00</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
@@ -12747,24 +12755,24 @@
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L163" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N163" s="2" t="inlineStr">
@@ -12781,14 +12789,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -12811,33 +12819,33 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 586,00</t>
+          <t>R$ 439,00</t>
         </is>
       </c>
       <c r="H164" s="3" t="inlineStr">
         <is>
-          <t>▼ 11,1%</t>
+          <t>▼ 25,1%</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>132</v>
-      </c>
-      <c r="J164" s="4" t="inlineStr">
-        <is>
-          <t>▲ 34,7%</t>
+        <v>131</v>
+      </c>
+      <c r="J164" s="3" t="inlineStr">
+        <is>
+          <t>▼ 0,8%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12854,14 +12862,14 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -12887,17 +12895,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H165" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J165" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J165" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
@@ -12927,14 +12935,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -12957,33 +12965,33 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 659,00</t>
-        </is>
-      </c>
-      <c r="H166" s="4" t="inlineStr">
-        <is>
-          <t>▲ 80,1%</t>
+          <t>R$ 586,00</t>
+        </is>
+      </c>
+      <c r="H166" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="J166" s="4" t="inlineStr">
         <is>
-          <t>▲ 3,2%</t>
+          <t>▲ 34,7%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -13000,14 +13008,14 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -13030,33 +13038,33 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
-        </is>
-      </c>
-      <c r="H167" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H167" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J167" s="4" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L167" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N167" s="2" t="inlineStr">
@@ -13073,14 +13081,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -13103,33 +13111,33 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>R$ 366,00</t>
-        </is>
-      </c>
-      <c r="H168" s="3" t="inlineStr">
-        <is>
-          <t>▼ 61,6%</t>
+          <t>R$ 659,00</t>
+        </is>
+      </c>
+      <c r="H168" s="4" t="inlineStr">
+        <is>
+          <t>▲ 80,1%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J168" s="4" t="inlineStr">
         <is>
-          <t>▲ 13,1%</t>
+          <t>▲ 3,2%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="L168" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -13146,14 +13154,14 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -13176,7 +13184,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 75,00</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -13185,24 +13193,24 @@
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J169" s="3" t="inlineStr">
-        <is>
-          <t>▼ 63,2%</t>
+        <v>8</v>
+      </c>
+      <c r="J169" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L169" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M169" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N169" s="2" t="inlineStr">
@@ -13219,14 +13227,14 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -13249,33 +13257,33 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>R$ 952,00</t>
-        </is>
-      </c>
-      <c r="H170" s="4" t="inlineStr">
-        <is>
-          <t>▲ 210,1%</t>
+          <t>R$ 366,00</t>
+        </is>
+      </c>
+      <c r="H170" s="3" t="inlineStr">
+        <is>
+          <t>▼ 61,6%</t>
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J170" s="4" t="inlineStr">
         <is>
-          <t>▲ 1,2%</t>
+          <t>▲ 13,1%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L170" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -13292,14 +13300,14 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -13331,11 +13339,11 @@
         </is>
       </c>
       <c r="I171" s="2" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
-          <t>▼ 26,9%</t>
+          <t>▼ 63,2%</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
@@ -13365,14 +13373,14 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -13395,33 +13403,33 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>R$ 307,00</t>
-        </is>
-      </c>
-      <c r="H172" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 952,00</t>
+        </is>
+      </c>
+      <c r="H172" s="4" t="inlineStr">
+        <is>
+          <t>▲ 210,1%</t>
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="J172" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>84</v>
+      </c>
+      <c r="J172" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1,2%</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="L172" s="2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
@@ -13438,14 +13446,14 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
           <t>BRINQ-019</t>
@@ -13477,11 +13485,11 @@
         </is>
       </c>
       <c r="I173" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>19</v>
+      </c>
+      <c r="J173" s="3" t="inlineStr">
+        <is>
+          <t>▼ 26,9%</t>
         </is>
       </c>
       <c r="K173" s="2" t="inlineStr">
@@ -13508,8 +13516,154 @@
         </is>
       </c>
     </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 307,00</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="L174" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O173"/>
+  <autoFilter ref="A1:O175"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-019-VASSOURA-INFANTIL-UNICORNIO.xlsx
+++ b/saida_skus/SKU_BRINQ-019-VASSOURA-INFANTIL-UNICORNIO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O175"/>
+  <dimension ref="A1:O183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -674,51 +674,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -790,12 +786,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -820,7 +816,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -828,51 +824,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I5" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>▲ 250,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -897,7 +889,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -905,10 +897,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -917,39 +907,37 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -974,7 +962,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -982,51 +970,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1098,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1128,7 +1112,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1136,10 +1120,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I9" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1148,39 +1130,37 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1205,7 +1185,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1213,8 +1193,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="2" t="n">
-        <v>0</v>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1223,37 +1205,39 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1325,12 +1309,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1402,12 +1386,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1479,12 +1463,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1556,12 +1540,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1633,12 +1617,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1663,7 +1647,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1671,8 +1655,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I16" s="2" t="n">
-        <v>0</v>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1681,37 +1667,39 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1783,12 +1771,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1813,7 +1801,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1821,10 +1809,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I18" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1833,39 +1819,37 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1937,12 +1921,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2014,12 +1998,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2091,12 +2075,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2168,12 +2152,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2245,12 +2229,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2275,7 +2259,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2283,10 +2267,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I24" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -2295,39 +2277,37 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2399,12 +2379,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2476,12 +2456,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2553,12 +2533,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2630,12 +2610,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2707,12 +2687,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2784,12 +2764,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2861,12 +2841,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2891,7 +2871,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2899,8 +2879,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I32" s="2" t="n">
-        <v>0</v>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2909,37 +2891,39 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3011,12 +2995,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3041,7 +3025,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3049,8 +3033,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I34" s="2" t="n">
-        <v>0</v>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -3059,37 +3045,39 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3161,12 +3149,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3191,7 +3179,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3199,8 +3187,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I36" s="2" t="n">
-        <v>0</v>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -3209,37 +3199,39 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3311,12 +3303,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3341,7 +3333,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3349,8 +3341,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I38" s="2" t="n">
-        <v>0</v>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -3359,37 +3353,39 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3461,12 +3457,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3491,7 +3487,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3499,10 +3495,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I40" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -3511,39 +3505,37 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3615,12 +3607,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3645,7 +3637,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3653,10 +3645,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I42" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -3665,39 +3655,37 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3769,12 +3757,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3799,7 +3787,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3807,10 +3795,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I44" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -3819,39 +3805,37 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3923,12 +3907,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3996,12 +3980,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4073,12 +4057,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4150,12 +4134,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4227,12 +4211,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4304,12 +4288,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4381,12 +4365,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4458,12 +4442,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4535,12 +4519,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4608,12 +4592,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4685,12 +4669,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4762,12 +4746,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4839,12 +4823,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4916,12 +4900,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4993,12 +4977,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5070,12 +5054,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5147,12 +5131,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5220,12 +5204,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5297,12 +5281,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5327,7 +5311,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5335,8 +5319,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I64" s="2" t="n">
-        <v>0</v>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5345,37 +5331,39 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5447,12 +5435,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5477,7 +5465,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5485,8 +5473,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I66" s="2" t="n">
-        <v>0</v>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -5495,37 +5485,39 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5597,12 +5589,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5627,7 +5619,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5635,8 +5627,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I68" s="2" t="n">
-        <v>0</v>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5645,37 +5639,39 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5747,12 +5743,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5777,7 +5773,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5785,10 +5781,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I70" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
@@ -5797,39 +5791,37 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5901,12 +5893,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5974,12 +5966,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6051,12 +6043,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6092,9 +6084,9 @@
       <c r="I74" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -6124,12 +6116,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6201,12 +6193,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6240,7 +6232,7 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
@@ -6274,12 +6266,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6351,12 +6343,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6381,7 +6373,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6389,47 +6381,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6501,12 +6497,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6540,7 +6536,7 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
@@ -6574,12 +6570,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6651,12 +6647,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6692,9 +6688,9 @@
       <c r="I82" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6724,12 +6720,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6801,12 +6797,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6840,7 +6836,7 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
@@ -6874,12 +6870,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6951,12 +6947,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6992,9 +6988,9 @@
       <c r="I86" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -7024,12 +7020,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7101,12 +7097,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7131,7 +7127,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -7139,10 +7135,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I88" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
@@ -7151,39 +7145,37 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7255,12 +7247,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7328,12 +7320,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7405,12 +7397,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7478,12 +7470,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7555,12 +7547,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7628,12 +7620,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7705,12 +7697,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7782,12 +7774,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7859,12 +7851,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7889,7 +7881,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -7897,10 +7889,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I98" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
@@ -7909,39 +7899,37 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -8013,12 +8001,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -8086,12 +8074,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8163,12 +8151,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8236,12 +8224,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8313,12 +8301,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8343,7 +8331,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -8351,8 +8339,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I104" s="2" t="n">
-        <v>0</v>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
@@ -8361,37 +8351,39 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L104" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8463,12 +8455,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8493,7 +8485,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -8501,47 +8493,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L106" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8613,12 +8609,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8652,7 +8648,7 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
@@ -8686,12 +8682,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8763,12 +8759,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8804,9 +8800,9 @@
       <c r="I110" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J110" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -8836,12 +8832,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8913,12 +8909,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8952,7 +8948,7 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
@@ -8986,12 +8982,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -9063,12 +9059,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -9104,9 +9100,9 @@
       <c r="I114" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -9136,12 +9132,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9213,12 +9209,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9252,7 +9248,7 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
@@ -9286,12 +9282,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9363,12 +9359,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9393,7 +9389,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -9401,51 +9397,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I118" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J118" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L118" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9517,12 +9509,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9556,7 +9548,7 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
@@ -9590,12 +9582,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9667,12 +9659,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9740,12 +9732,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9817,12 +9809,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9858,9 +9850,9 @@
       <c r="I124" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J124" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9890,12 +9882,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9967,12 +9959,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9997,7 +9989,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -10005,8 +9997,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I126" s="2" t="n">
-        <v>1</v>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
@@ -10015,37 +10009,39 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L126" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -10117,12 +10113,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -10150,17 +10146,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H128" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J128" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -10190,12 +10186,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10267,12 +10263,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -10297,7 +10293,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -10306,7 +10302,7 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
@@ -10315,15 +10311,15 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -10340,12 +10336,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10417,12 +10413,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10450,9 +10446,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H132" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
@@ -10490,12 +10486,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10567,12 +10563,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10597,16 +10593,16 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
-        </is>
-      </c>
-      <c r="H134" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
@@ -10615,15 +10611,15 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L134" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -10640,12 +10636,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10717,12 +10713,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10747,12 +10743,12 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>R$ 312,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H136" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I136" s="2" t="n">
@@ -10769,11 +10765,11 @@
         </is>
       </c>
       <c r="L136" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -10790,12 +10786,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10867,12 +10863,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -10897,33 +10893,33 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>R$ 390,00</t>
-        </is>
-      </c>
-      <c r="H138" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+          <t>R$ 78,00</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="J138" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,6%</t>
+        <v>7</v>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L138" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -10940,12 +10936,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -11017,12 +11013,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -11047,33 +11043,33 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>R$ 234,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H140" s="3" t="inlineStr">
         <is>
-          <t>▼ 49,9%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>▼ 28,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L140" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -11090,12 +11086,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -11167,12 +11163,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -11197,33 +11193,33 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>R$ 467,00</t>
-        </is>
-      </c>
-      <c r="H142" s="4" t="inlineStr">
-        <is>
-          <t>▲ 199,4%</t>
+          <t>R$ 78,00</t>
+        </is>
+      </c>
+      <c r="H142" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="J142" s="4" t="inlineStr">
-        <is>
-          <t>▲ 49,2%</t>
+        <v>15</v>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L142" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -11240,12 +11236,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11317,12 +11313,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -11347,33 +11343,33 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>R$ 156,00</t>
+          <t>R$ 312,00</t>
         </is>
       </c>
       <c r="H144" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
-          <t>▼ 19,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L144" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -11390,12 +11386,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11467,12 +11463,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11497,33 +11493,33 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>R$ 234,00</t>
-        </is>
-      </c>
-      <c r="H146" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,9%</t>
+          <t>R$ 390,00</t>
+        </is>
+      </c>
+      <c r="H146" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
-          <t>▼ 2,6%</t>
+          <t>▼ 4,6%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="L146" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -11540,12 +11536,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11617,12 +11613,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11647,33 +11643,33 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>R$ 467,00</t>
+          <t>R$ 234,00</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 49,9%</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
-          <t>▼ 27,1%</t>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L148" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -11690,12 +11686,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11767,12 +11763,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -11797,33 +11793,33 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>R$ 545,00</t>
+          <t>R$ 467,00</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
-          <t>▲ 74,7%</t>
+          <t>▲ 199,4%</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="J150" s="4" t="inlineStr">
         <is>
-          <t>▲ 10,3%</t>
+          <t>▲ 49,2%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="L150" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -11840,12 +11836,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11870,7 +11866,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -11878,8 +11874,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I151" s="2" t="n">
-        <v>0</v>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
@@ -11888,37 +11886,39 @@
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L151" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -11943,33 +11943,33 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>R$ 312,00</t>
-        </is>
-      </c>
-      <c r="H152" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 156,00</t>
+        </is>
+      </c>
+      <c r="H152" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>97</v>
-      </c>
-      <c r="J152" s="4" t="inlineStr">
-        <is>
-          <t>▲ 203,1%</t>
+        <v>61</v>
+      </c>
+      <c r="J152" s="3" t="inlineStr">
+        <is>
+          <t>▼ 19,7%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L152" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -11986,12 +11986,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -12016,7 +12016,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -12024,8 +12024,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I153" s="2" t="n">
-        <v>0</v>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
@@ -12034,37 +12036,39 @@
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L153" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O153" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -12089,38 +12093,38 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
-        </is>
-      </c>
-      <c r="H154" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 234,00</t>
+        </is>
+      </c>
+      <c r="H154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,9%</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J154" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1500,0%</t>
+        <v>76</v>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 2,6%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O154" s="2" t="inlineStr">
@@ -12132,12 +12136,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -12162,7 +12166,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -12170,47 +12174,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I155" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J155" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L155" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O155" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -12235,33 +12243,33 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 467,00</t>
+        </is>
+      </c>
+      <c r="H156" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J156" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>78</v>
+      </c>
+      <c r="J156" s="3" t="inlineStr">
+        <is>
+          <t>▼ 27,1%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L156" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -12278,12 +12286,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12308,55 +12316,59 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H157" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I157" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J157" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L157" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -12381,33 +12393,33 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H158" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 545,00</t>
+        </is>
+      </c>
+      <c r="H158" s="4" t="inlineStr">
+        <is>
+          <t>▲ 74,7%</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J158" s="3" t="inlineStr">
-        <is>
-          <t>▼ 99,2%</t>
+        <v>107</v>
+      </c>
+      <c r="J158" s="4" t="inlineStr">
+        <is>
+          <t>▲ 10,3%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12424,12 +12436,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12454,7 +12466,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -12463,7 +12475,7 @@
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
@@ -12472,15 +12484,15 @@
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L159" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
@@ -12497,12 +12509,12 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -12527,33 +12539,33 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 659,00</t>
+          <t>R$ 312,00</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr">
         <is>
-          <t>▲ 124,9%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="J160" s="4" t="inlineStr">
         <is>
-          <t>▲ 4,3%</t>
+          <t>▲ 203,1%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12570,12 +12582,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12603,17 +12615,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H161" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I161" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J161" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -12643,12 +12655,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -12673,33 +12685,33 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 293,00</t>
-        </is>
-      </c>
-      <c r="H162" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 78,00</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>115</v>
-      </c>
-      <c r="J162" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,2%</t>
+        <v>32</v>
+      </c>
+      <c r="J162" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1500,0%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12716,12 +12728,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12746,7 +12758,7 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
@@ -12755,24 +12767,24 @@
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
-          <t>▼ 12,5%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L163" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N163" s="2" t="inlineStr">
@@ -12789,12 +12801,12 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -12819,33 +12831,33 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 439,00</t>
-        </is>
-      </c>
-      <c r="H164" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>131</v>
-      </c>
-      <c r="J164" s="3" t="inlineStr">
-        <is>
-          <t>▼ 0,8%</t>
+        <v>2</v>
+      </c>
+      <c r="J164" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12862,12 +12874,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12895,17 +12907,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H165" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H165" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J165" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J165" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
@@ -12935,12 +12947,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -12965,33 +12977,33 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 586,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>▼ 11,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>132</v>
-      </c>
-      <c r="J166" s="4" t="inlineStr">
-        <is>
-          <t>▲ 34,7%</t>
+        <v>1</v>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>▼ 99,2%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -13008,12 +13020,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -13038,33 +13050,33 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H167" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 75,00</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J167" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L167" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N167" s="2" t="inlineStr">
@@ -13081,12 +13093,12 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -13116,20 +13128,20 @@
       </c>
       <c r="H168" s="4" t="inlineStr">
         <is>
-          <t>▲ 80,1%</t>
+          <t>▲ 124,9%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="J168" s="4" t="inlineStr">
         <is>
-          <t>▲ 3,2%</t>
+          <t>▲ 4,3%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="L168" s="2" t="n">
@@ -13137,7 +13149,7 @@
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -13154,12 +13166,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -13184,33 +13196,33 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
-        </is>
-      </c>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H169" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J169" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J169" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L169" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M169" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N169" s="2" t="inlineStr">
@@ -13227,12 +13239,12 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -13257,38 +13269,38 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>R$ 366,00</t>
+          <t>R$ 293,00</t>
         </is>
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>▼ 61,6%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>95</v>
-      </c>
-      <c r="J170" s="4" t="inlineStr">
-        <is>
-          <t>▲ 13,1%</t>
+        <v>115</v>
+      </c>
+      <c r="J170" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,2%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="L170" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O170" s="2" t="inlineStr">
@@ -13300,12 +13312,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -13330,7 +13342,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 75,00</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -13343,20 +13355,20 @@
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
-          <t>▼ 63,2%</t>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L171" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M171" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N171" s="2" t="inlineStr">
@@ -13373,12 +13385,12 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -13403,33 +13415,33 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>R$ 952,00</t>
-        </is>
-      </c>
-      <c r="H172" s="4" t="inlineStr">
-        <is>
-          <t>▲ 210,1%</t>
+          <t>R$ 439,00</t>
+        </is>
+      </c>
+      <c r="H172" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,1%</t>
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>84</v>
-      </c>
-      <c r="J172" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1,2%</t>
+        <v>131</v>
+      </c>
+      <c r="J172" s="3" t="inlineStr">
+        <is>
+          <t>▼ 0,8%</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L172" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
@@ -13446,12 +13458,12 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -13485,11 +13497,11 @@
         </is>
       </c>
       <c r="I173" s="2" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
-          <t>▼ 26,9%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K173" s="2" t="inlineStr">
@@ -13519,12 +13531,12 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -13549,33 +13561,33 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>R$ 307,00</t>
-        </is>
-      </c>
-      <c r="H174" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 586,00</t>
+        </is>
+      </c>
+      <c r="H174" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="I174" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="J174" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>132</v>
+      </c>
+      <c r="J174" s="4" t="inlineStr">
+        <is>
+          <t>▲ 34,7%</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L174" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="N174" s="2" t="inlineStr">
@@ -13592,12 +13604,12 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
@@ -13625,17 +13637,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H175" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I175" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>10</v>
+      </c>
+      <c r="J175" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K175" s="2" t="inlineStr">
@@ -13662,8 +13674,592 @@
         </is>
       </c>
     </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 659,00</t>
+        </is>
+      </c>
+      <c r="H176" s="4" t="inlineStr">
+        <is>
+          <t>▲ 80,1%</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="J176" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3,2%</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>9,2%</t>
+        </is>
+      </c>
+      <c r="L176" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>6,3%</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>R$ 75,00</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J177" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L177" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 366,00</t>
+        </is>
+      </c>
+      <c r="H178" s="3" t="inlineStr">
+        <is>
+          <t>▼ 61,6%</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="J178" s="4" t="inlineStr">
+        <is>
+          <t>▲ 13,1%</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>5,3%</t>
+        </is>
+      </c>
+      <c r="L178" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J179" s="3" t="inlineStr">
+        <is>
+          <t>▼ 63,2%</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L179" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 952,00</t>
+        </is>
+      </c>
+      <c r="H180" s="4" t="inlineStr">
+        <is>
+          <t>▲ 210,1%</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="J180" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1,2%</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>15,5%</t>
+        </is>
+      </c>
+      <c r="L180" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>11,3%</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="J181" s="3" t="inlineStr">
+        <is>
+          <t>▼ 26,9%</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L181" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>3076915307</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 77,90</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 307,00</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="L182" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-019</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Vassoura infantil unicornio</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>6311164080</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,80</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L183" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M183" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O183" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O175"/>
+  <autoFilter ref="A1:O183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>